--- a/finance/GreetHub_Financial_Model.xlsx
+++ b/finance/GreetHub_Financial_Model.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="172" formatCode="$#,##0.000;($#,##0.000);-"/>
     <numFmt numFmtId="173" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +73,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -116,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,6 +156,8 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,7 +168,6 @@
     </xf>
     <xf numFmtId="17" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -2202,7 +2209,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
@@ -2211,17 +2218,17 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>ESTIMATE</t>
+          <t>CTO PLANNING FIGURE</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>15%-60%</t>
+          <t>10%-40%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Includes auto-QA retries.</t>
+          <t>CTO planning figure 20% (2 of 8 real 2K pages failed QA first pass; small sample).</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2239,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
@@ -2241,17 +2248,17 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>ESTIMATE</t>
+          <t>CTO PLANNING FIGURE</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>5%-30%</t>
+          <t>10%-35%</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Eye Story: ~16 renders incl. reroll allowance for a 14-page book.</t>
+          <t>CTO planning figure 20%; small sample.</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4196,7 @@
         <v/>
       </c>
       <c r="G5" s="21">
-        <f>'Model Costs'!J27*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>'Model Costs'!J35*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="H5" s="21">
@@ -4251,7 +4258,7 @@
         <v/>
       </c>
       <c r="G6" s="21">
-        <f>'Model Costs'!J28*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>'Model Costs'!J36*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="H6" s="21">
@@ -4313,7 +4320,7 @@
         <v/>
       </c>
       <c r="G7" s="21">
-        <f>'Model Costs'!J29*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>'Model Costs'!J37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="H7" s="21">
@@ -4375,7 +4382,7 @@
         <v/>
       </c>
       <c r="G8" s="21">
-        <f>'Model Costs'!J30*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>'Model Costs'!J38*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="H8" s="21">
@@ -4437,7 +4444,7 @@
         <v/>
       </c>
       <c r="G9" s="21">
-        <f>'Model Costs'!J31*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>'Model Costs'!J39*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="H9" s="21">
@@ -4968,7 +4975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4976,11 +4983,12 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4991,515 +4999,459 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Blue = ESTIMATE input. Yellow = paste CTO measured values from finance/measured_costs.json (blank = use estimate). Active = measured if present, else estimate. Exception to 'inputs only on Inputs': the CTO swap-in slots live here by owner request.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>MEASURED = CTO pipeline ledger (finance/measured_costs.json, OpenRouter usage.cost, 4 runs, $1.53 test spend). EXTRAPOLATED = CTO scaled measured per-call costs linearly to full 24/32-page books (no full-book run yet). ESTIMATE = my assumption, not measured. Yellow = pasted CTO data (blank = fall back to estimate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Exception to 'inputs only on Inputs': the CTO swap-in slots and cost tables live here by owner request. Image size selector below chooses 2K (CTO default, measured totals apply) or 4K (totals recomputed from the 4K per-call price).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Print image size (2K or 4K)</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2K = about 280 DPI at card size and 234 DPI at book size (CTO). Below the 300 DPI print norm but CTO judges 4K (2x cost) gives little visible gain. Verify with a physical Lulu proof and the Lulu file validator before launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Unit price</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Estimate</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Estimate (superseded)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Measured (CTO paste)</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Image render, 4K print page (Gemini image via OpenRouter)</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="C5" s="32" t="n"/>
-      <c r="D5" s="33">
-        <f>IF(ISNUMBER(C5),C5,B5)</f>
-        <v/>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>$ / render</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Eye Story build: ~30 renders = $3.50 (~$0.117). Owner: ~$0.11.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Image render, guest preview (low-res, watermarked)</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="33">
-        <f>IF(ISNUMBER(C6),C6,B6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>$ / render</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>GUESS: 1K render cheaper than 4K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Vision QA check (cheap model) per render</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="33">
-        <f>IF(ISNUMBER(C7),C7,B7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>$ / call</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>GUESS; PLAN.md stage 6.</t>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Status / source</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Claude Sonnet input</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="21">
+          <t>Image render 2K (nano-banana-2.1 via OpenRouter)</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="D8" s="35">
         <f>IF(ISNUMBER(C8),C8,B8)</f>
         <v/>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>$ / M tokens</t>
+          <t>$ / render</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Anthropic list price - verify.</t>
+          <t>MEASURED, n=14. Old estimate $0.11 was a 4K-class figure from the Eye Story.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Claude Sonnet output</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="21">
+          <t>Image render 4K</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="D9" s="35">
         <f>IF(ISNUMBER(C9),C9,B9)</f>
         <v/>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>$ / render</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>MEASURED, n=1 (single probe call).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Image render 1K (guest preview)</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="D10" s="35">
+        <f>IF(ISNUMBER(C10),C10,B10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>$ / render</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>MEASURED, n=5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Vision QA check per render</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="D11" s="35">
+        <f>IF(ISNUMBER(C11),C11,B11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>$ / call</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>MEASURED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Claude Sonnet input (for unmeasured intake chat)</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="21">
+        <f>IF(ISNUMBER(C12),C12,B12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>$ / M tokens</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Anthropic list price - verify.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Text calls (Claude Sonnet): tokens per call, then cost per call</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Call type</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Intake chat (card)</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Intake chat (book)</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Story writer (book)</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Identity sheet (vision)</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>Art-director page prompts (book)</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Card prompts + message</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>Guest intake (mini)</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ESTIMATE: list price - verify.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Input tokens / call (ESTIMATE)</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
+          <t>Claude Sonnet output (for unmeasured intake chat)</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="21">
+        <f>IF(ISNUMBER(C13),C13,B13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>$ / M tokens</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>ESTIMATE: list price - verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Render price used (follows size selector)</t>
+        </is>
+      </c>
+      <c r="D14" s="36">
+        <f>IF($B$5="4K",$D$9,$D$8)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>$ / render</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Text calls: estimate from tokens, then CTO measured cost per unit</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Call type</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Intake chat (card)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Intake chat (book)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Story writer (per spread)</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Identity sheet (vision)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Art-director prompts (per page)</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Card copy + prompts (per card)</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Guest intake (mini)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Input tokens / unit (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
         <v>14000</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C18" s="14" t="n">
         <v>22000</v>
       </c>
-      <c r="D13" s="14" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E13" s="14" t="n">
+      <c r="D18" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="E18" s="14" t="n">
         <v>6000</v>
       </c>
-      <c r="F13" s="14" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G13" s="14" t="n">
+      <c r="F18" s="14" t="n">
+        <v>900</v>
+      </c>
+      <c r="G18" s="14" t="n">
         <v>4500</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H18" s="14" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Output tokens / call (ESTIMATE)</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Output tokens / unit (ESTIMATE)</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
         <v>1800</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C19" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="D14" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E14" s="14" t="n">
+      <c r="D19" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="E19" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="F14" s="14" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G14" s="14" t="n">
+      <c r="F19" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="G19" s="14" t="n">
         <v>1300</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H19" s="14" t="n">
         <v>800</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Cost per call ($)</t>
-        </is>
-      </c>
-      <c r="B15" s="33">
-        <f>B13/1000000*$D$8+B14/1000000*$D$9</f>
-        <v/>
-      </c>
-      <c r="C15" s="33">
-        <f>C13/1000000*$D$8+C14/1000000*$D$9</f>
-        <v/>
-      </c>
-      <c r="D15" s="33">
-        <f>D13/1000000*$D$8+D14/1000000*$D$9</f>
-        <v/>
-      </c>
-      <c r="E15" s="33">
-        <f>E13/1000000*$D$8+E14/1000000*$D$9</f>
-        <v/>
-      </c>
-      <c r="F15" s="33">
-        <f>F13/1000000*$D$8+F14/1000000*$D$9</f>
-        <v/>
-      </c>
-      <c r="G15" s="33">
-        <f>G13/1000000*$D$8+G14/1000000*$D$9</f>
-        <v/>
-      </c>
-      <c r="H15" s="33">
-        <f>H13/1000000*$D$8+H14/1000000*$D$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Calls per SKU (count of each call type; ESTIMATE)</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Intake chat (card)</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Intake chat (book)</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Story writer (book)</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Identity sheet (vision)</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Art-director page prompts (book)</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Card prompts + message</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>Guest intake (mini)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5">
-        <f>Inputs!A47</f>
-        <v/>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="5">
-        <f>Inputs!A48</f>
-        <v/>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>0</v>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Estimated cost per unit ($)</t>
+        </is>
+      </c>
+      <c r="B20" s="35">
+        <f>B18/1000000*$D$12+B19/1000000*$D$13</f>
+        <v/>
+      </c>
+      <c r="C20" s="35">
+        <f>C18/1000000*$D$12+C19/1000000*$D$13</f>
+        <v/>
+      </c>
+      <c r="D20" s="35">
+        <f>D18/1000000*$D$12+D19/1000000*$D$13</f>
+        <v/>
+      </c>
+      <c r="E20" s="35">
+        <f>E18/1000000*$D$12+E19/1000000*$D$13</f>
+        <v/>
+      </c>
+      <c r="F20" s="35">
+        <f>F18/1000000*$D$12+F19/1000000*$D$13</f>
+        <v/>
+      </c>
+      <c r="G20" s="35">
+        <f>G18/1000000*$D$12+G19/1000000*$D$13</f>
+        <v/>
+      </c>
+      <c r="H20" s="35">
+        <f>H18/1000000*$D$12+H19/1000000*$D$13</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5">
-        <f>Inputs!A49</f>
-        <v/>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>MEASURED cost per unit (CTO paste)</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="34" t="n"/>
+      <c r="D21" s="34" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="E21" s="34" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="G21" s="34" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="H21" s="34" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5">
-        <f>Inputs!A50</f>
-        <v/>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>0</v>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Cost per unit used ($)</t>
+        </is>
+      </c>
+      <c r="B22" s="36">
+        <f>IF(ISNUMBER(B21),B21,B20)</f>
+        <v/>
+      </c>
+      <c r="C22" s="36">
+        <f>IF(ISNUMBER(C21),C21,C20)</f>
+        <v/>
+      </c>
+      <c r="D22" s="36">
+        <f>IF(ISNUMBER(D21),D21,D20)</f>
+        <v/>
+      </c>
+      <c r="E22" s="36">
+        <f>IF(ISNUMBER(E21),E21,E20)</f>
+        <v/>
+      </c>
+      <c r="F22" s="36">
+        <f>IF(ISNUMBER(F21),F21,F20)</f>
+        <v/>
+      </c>
+      <c r="G22" s="36">
+        <f>IF(ISNUMBER(G21),G21,G20)</f>
+        <v/>
+      </c>
+      <c r="H22" s="36">
+        <f>IF(ISNUMBER(H21),H21,H20)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5">
-        <f>Inputs!A51</f>
-        <v/>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>0</v>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Measured: identity 0.0106, story 0.0074 per spread, prompts 0.0094 per page, card copy 0.0054 + card prompts 0.0417. Intake chat and guest intake are NOT measured (Greet Guide not built).</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Token cost per SKU (before scenario multiplier and OpenRouter fee)</t>
+          <t>Units per SKU (ESTIMATE; spreads/pages per CTO: 24pp = 11 spreads, 14 renders; 32pp = 15 spreads, 18 renders)</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
@@ -5520,47 +5472,37 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Base renders (ESTIMATE)</t>
+          <t>Intake chat (card)</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Re-roll rate</t>
+          <t>Intake chat (book)</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Effective renders</t>
+          <t>Story writer (per spread)</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Render $</t>
+          <t>Identity sheet (vision)</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>QA $</t>
+          <t>Art-director prompts (per page)</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Text (Sonnet) $</t>
+          <t>Card copy + prompts (per card)</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>Computed total $</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Measured total $ (CTO paste)</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>Token cost used $</t>
+          <t>Guest intake (mini)</t>
         </is>
       </c>
     </row>
@@ -5570,36 +5512,25 @@
         <v/>
       </c>
       <c r="B27" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" s="22">
-        <f>IF(Inputs!B47="Card",Inputs!$B$34,Inputs!$B$35)</f>
-        <v/>
-      </c>
-      <c r="D27" s="28">
-        <f>B27*(1+C27)</f>
-        <v/>
-      </c>
-      <c r="E27" s="33">
-        <f>D27*$D$5</f>
-        <v/>
-      </c>
-      <c r="F27" s="33">
-        <f>D27*$D$7</f>
-        <v/>
-      </c>
-      <c r="G27" s="33">
-        <f>SUMPRODUCT(B19:H19,$B$15:$H$15)</f>
-        <v/>
-      </c>
-      <c r="H27" s="33">
-        <f>E27+F27+G27</f>
-        <v/>
-      </c>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="34">
-        <f>IF(ISNUMBER(I27),I27,H27)</f>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -5608,36 +5539,25 @@
         <v/>
       </c>
       <c r="B28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="22">
-        <f>IF(Inputs!B48="Card",Inputs!$B$34,Inputs!$B$35)</f>
-        <v/>
-      </c>
-      <c r="D28" s="28">
-        <f>B28*(1+C28)</f>
-        <v/>
-      </c>
-      <c r="E28" s="33">
-        <f>D28*$D$5</f>
-        <v/>
-      </c>
-      <c r="F28" s="33">
-        <f>D28*$D$7</f>
-        <v/>
-      </c>
-      <c r="G28" s="33">
-        <f>SUMPRODUCT(B20:H20,$B$15:$H$15)</f>
-        <v/>
-      </c>
-      <c r="H28" s="33">
-        <f>E28+F28+G28</f>
-        <v/>
-      </c>
-      <c r="I28" s="32" t="n"/>
-      <c r="J28" s="34">
-        <f>IF(ISNUMBER(I28),I28,H28)</f>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -5646,36 +5566,25 @@
         <v/>
       </c>
       <c r="B29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="C29" s="22">
-        <f>IF(Inputs!B49="Card",Inputs!$B$34,Inputs!$B$35)</f>
-        <v/>
-      </c>
-      <c r="D29" s="28">
-        <f>B29*(1+C29)</f>
-        <v/>
-      </c>
-      <c r="E29" s="33">
-        <f>D29*$D$5</f>
-        <v/>
-      </c>
-      <c r="F29" s="33">
-        <f>D29*$D$7</f>
-        <v/>
-      </c>
-      <c r="G29" s="33">
-        <f>SUMPRODUCT(B21:H21,$B$15:$H$15)</f>
-        <v/>
-      </c>
-      <c r="H29" s="33">
-        <f>E29+F29+G29</f>
-        <v/>
-      </c>
-      <c r="I29" s="32" t="n"/>
-      <c r="J29" s="34">
-        <f>IF(ISNUMBER(I29),I29,H29)</f>
-        <v/>
+      <c r="E29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -5684,36 +5593,25 @@
         <v/>
       </c>
       <c r="B30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="C30" s="22">
-        <f>IF(Inputs!B50="Card",Inputs!$B$34,Inputs!$B$35)</f>
-        <v/>
-      </c>
-      <c r="D30" s="28">
-        <f>B30*(1+C30)</f>
-        <v/>
-      </c>
-      <c r="E30" s="33">
-        <f>D30*$D$5</f>
-        <v/>
-      </c>
-      <c r="F30" s="33">
-        <f>D30*$D$7</f>
-        <v/>
-      </c>
-      <c r="G30" s="33">
-        <f>SUMPRODUCT(B22:H22,$B$15:$H$15)</f>
-        <v/>
-      </c>
-      <c r="H30" s="33">
-        <f>E30+F30+G30</f>
-        <v/>
-      </c>
-      <c r="I30" s="32" t="n"/>
-      <c r="J30" s="34">
-        <f>IF(ISNUMBER(I30),I30,H30)</f>
-        <v/>
+      <c r="E30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -5722,42 +5620,31 @@
         <v/>
       </c>
       <c r="B31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="C31" s="22">
-        <f>IF(Inputs!B51="Card",Inputs!$B$34,Inputs!$B$35)</f>
-        <v/>
-      </c>
-      <c r="D31" s="28">
-        <f>B31*(1+C31)</f>
-        <v/>
-      </c>
-      <c r="E31" s="33">
-        <f>D31*$D$5</f>
-        <v/>
-      </c>
-      <c r="F31" s="33">
-        <f>D31*$D$7</f>
-        <v/>
-      </c>
-      <c r="G31" s="33">
-        <f>SUMPRODUCT(B23:H23,$B$15:$H$15)</f>
-        <v/>
-      </c>
-      <c r="H31" s="33">
-        <f>E31+F31+G31</f>
-        <v/>
-      </c>
-      <c r="I31" s="32" t="n"/>
-      <c r="J31" s="34">
-        <f>IF(ISNUMBER(I31),I31,H31)</f>
-        <v/>
+      <c r="E31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Guest free preview (cost with no revenue)</t>
+          <t>Token cost per SKU (before scenario multiplier and OpenRouter fee)</t>
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
@@ -5769,55 +5656,369 @@
       <c r="H33" s="8" t="n"/>
       <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Renders per guest preview</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="n">
+      <c r="K33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="55" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Base renders (CTO)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Re-roll rate</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Effective renders</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Render $</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>QA $</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Text $</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Computed total $</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Measured total $ with re-rolls (CTO paste, 2K)</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>Token cost used $</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>Basis of measured figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5">
+        <f>Inputs!A47</f>
+        <v/>
+      </c>
+      <c r="B35" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="22">
+        <f>IF(Inputs!B47="Card",Inputs!$B$34,Inputs!$B$35)</f>
+        <v/>
+      </c>
+      <c r="D35" s="28">
+        <f>B35*(1+C35)</f>
+        <v/>
+      </c>
+      <c r="E35" s="35">
+        <f>D35*$D$14</f>
+        <v/>
+      </c>
+      <c r="F35" s="35">
+        <f>D35*$D$11</f>
+        <v/>
+      </c>
+      <c r="G35" s="35">
+        <f>SUMPRODUCT(B27:H27,$B$22:$H$22)</f>
+        <v/>
+      </c>
+      <c r="H35" s="35">
+        <f>E35+F35+G35</f>
+        <v/>
+      </c>
+      <c r="I35" s="34" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="J35" s="36">
+        <f>IF(AND($B$5="2K",ISNUMBER(I35)),I35,H35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED from per-call costs; clean 3-render run measured $0.239</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5">
+        <f>Inputs!A48</f>
+        <v/>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="22">
+        <f>IF(Inputs!B48="Card",Inputs!$B$34,Inputs!$B$35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="28">
+        <f>B36*(1+C36)</f>
+        <v/>
+      </c>
+      <c r="E36" s="35">
+        <f>D36*$D$14</f>
+        <v/>
+      </c>
+      <c r="F36" s="35">
+        <f>D36*$D$11</f>
+        <v/>
+      </c>
+      <c r="G36" s="35">
+        <f>SUMPRODUCT(B28:H28,$B$22:$H$22)</f>
+        <v/>
+      </c>
+      <c r="H36" s="35">
+        <f>E36+F36+G36</f>
+        <v/>
+      </c>
+      <c r="I36" s="34" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="J36" s="36">
+        <f>IF(AND($B$5="2K",ISNUMBER(I36)),I36,H36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED (same as digital card)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5">
+        <f>Inputs!A49</f>
+        <v/>
+      </c>
+      <c r="B37" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C37" s="22">
+        <f>IF(Inputs!B49="Card",Inputs!$B$34,Inputs!$B$35)</f>
+        <v/>
+      </c>
+      <c r="D37" s="28">
+        <f>B37*(1+C37)</f>
+        <v/>
+      </c>
+      <c r="E37" s="35">
+        <f>D37*$D$14</f>
+        <v/>
+      </c>
+      <c r="F37" s="35">
+        <f>D37*$D$11</f>
+        <v/>
+      </c>
+      <c r="G37" s="35">
+        <f>SUMPRODUCT(B29:H29,$B$22:$H$22)</f>
+        <v/>
+      </c>
+      <c r="H37" s="35">
+        <f>E37+F37+G37</f>
+        <v/>
+      </c>
+      <c r="I37" s="34" t="n">
+        <v>1.2641</v>
+      </c>
+      <c r="J37" s="36">
+        <f>IF(AND($B$5="2K",ISNUMBER(I37)),I37,H37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED, 24pp book (4-art-page run measured $0.469, not a full book)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5">
+        <f>Inputs!A50</f>
+        <v/>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" s="22">
+        <f>IF(Inputs!B50="Card",Inputs!$B$34,Inputs!$B$35)</f>
+        <v/>
+      </c>
+      <c r="D38" s="28">
+        <f>B38*(1+C38)</f>
+        <v/>
+      </c>
+      <c r="E38" s="35">
+        <f>D38*$D$14</f>
+        <v/>
+      </c>
+      <c r="F38" s="35">
+        <f>D38*$D$11</f>
+        <v/>
+      </c>
+      <c r="G38" s="35">
+        <f>SUMPRODUCT(B30:H30,$B$22:$H$22)</f>
+        <v/>
+      </c>
+      <c r="H38" s="35">
+        <f>E38+F38+G38</f>
+        <v/>
+      </c>
+      <c r="I38" s="34" t="n">
+        <v>1.2641</v>
+      </c>
+      <c r="J38" s="36">
+        <f>IF(AND($B$5="2K",ISNUMBER(I38)),I38,H38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED, no full 24pp run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5">
+        <f>Inputs!A51</f>
+        <v/>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C39" s="22">
+        <f>IF(Inputs!B51="Card",Inputs!$B$34,Inputs!$B$35)</f>
+        <v/>
+      </c>
+      <c r="D39" s="28">
+        <f>B39*(1+C39)</f>
+        <v/>
+      </c>
+      <c r="E39" s="35">
+        <f>D39*$D$14</f>
+        <v/>
+      </c>
+      <c r="F39" s="35">
+        <f>D39*$D$11</f>
+        <v/>
+      </c>
+      <c r="G39" s="35">
+        <f>SUMPRODUCT(B31:H31,$B$22:$H$22)</f>
+        <v/>
+      </c>
+      <c r="H39" s="35">
+        <f>E39+F39+G39</f>
+        <v/>
+      </c>
+      <c r="I39" s="34" t="n">
+        <v>1.6357</v>
+      </c>
+      <c r="J39" s="36">
+        <f>IF(AND($B$5="2K",ISNUMBER(I39)),I39,H39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EXTRAPOLATED, no full 32pp run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>At 2K the CTO measured/extrapolated total is used. At 4K the totals are recomputed from the 4K render price (pasted totals are 2K only). CTO reference for 24pp at 4K: $2.31 with re-rolls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Guest free preview (cost with no revenue)</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Renders per guest preview (1K)</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Guest preview cost, computed $</t>
         </is>
       </c>
-      <c r="B35" s="33">
-        <f>B34*$D$6+H15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Guest preview cost, measured $ (CTO paste)</t>
-        </is>
-      </c>
-      <c r="B36" s="32" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="B44" s="35">
+        <f>B43*$D$10+H22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Guest preview cost, CTO estimate $ (not run end to end)</t>
+        </is>
+      </c>
+      <c r="B45" s="34" t="n">
+        <v>0.0689</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Guest preview cost used $</t>
         </is>
       </c>
-      <c r="B37" s="34">
-        <f>IF(ISNUMBER(B36),B36,B35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Reference: PLAN.md expects ~$2-4 per book and ~$0.30-0.60 per card. Scenario token multiplier and OpenRouter fee are applied on Unit Economics.</t>
+      <c r="B46" s="36">
+        <f>IF(ISNUMBER(B45),B45,B44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Scenario token multiplier and the OpenRouter fee are applied on Unit Economics.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"2K,4K"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6089,147 +6290,147 @@
           <t>Month #</t>
         </is>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="37">
         <f>Forecast!D6</f>
         <v/>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="37">
         <f>Forecast!E6</f>
         <v/>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="37">
         <f>Forecast!F6</f>
         <v/>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="37">
         <f>Forecast!G6</f>
         <v/>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="37">
         <f>Forecast!H6</f>
         <v/>
       </c>
-      <c r="I5" s="35">
+      <c r="I5" s="37">
         <f>Forecast!I6</f>
         <v/>
       </c>
-      <c r="J5" s="35">
+      <c r="J5" s="37">
         <f>Forecast!J6</f>
         <v/>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="37">
         <f>Forecast!K6</f>
         <v/>
       </c>
-      <c r="L5" s="35">
+      <c r="L5" s="37">
         <f>Forecast!L6</f>
         <v/>
       </c>
-      <c r="M5" s="35">
+      <c r="M5" s="37">
         <f>Forecast!M6</f>
         <v/>
       </c>
-      <c r="N5" s="35">
+      <c r="N5" s="37">
         <f>Forecast!N6</f>
         <v/>
       </c>
-      <c r="O5" s="35">
+      <c r="O5" s="37">
         <f>Forecast!O6</f>
         <v/>
       </c>
-      <c r="P5" s="35">
+      <c r="P5" s="37">
         <f>Forecast!P6</f>
         <v/>
       </c>
-      <c r="Q5" s="35">
+      <c r="Q5" s="37">
         <f>Forecast!Q6</f>
         <v/>
       </c>
-      <c r="R5" s="35">
+      <c r="R5" s="37">
         <f>Forecast!R6</f>
         <v/>
       </c>
-      <c r="S5" s="35">
+      <c r="S5" s="37">
         <f>Forecast!S6</f>
         <v/>
       </c>
-      <c r="T5" s="35">
+      <c r="T5" s="37">
         <f>Forecast!T6</f>
         <v/>
       </c>
-      <c r="U5" s="35">
+      <c r="U5" s="37">
         <f>Forecast!U6</f>
         <v/>
       </c>
-      <c r="V5" s="35">
+      <c r="V5" s="37">
         <f>Forecast!V6</f>
         <v/>
       </c>
-      <c r="W5" s="35">
+      <c r="W5" s="37">
         <f>Forecast!W6</f>
         <v/>
       </c>
-      <c r="X5" s="35">
+      <c r="X5" s="37">
         <f>Forecast!X6</f>
         <v/>
       </c>
-      <c r="Y5" s="35">
+      <c r="Y5" s="37">
         <f>Forecast!Y6</f>
         <v/>
       </c>
-      <c r="Z5" s="35">
+      <c r="Z5" s="37">
         <f>Forecast!Z6</f>
         <v/>
       </c>
-      <c r="AA5" s="35">
+      <c r="AA5" s="37">
         <f>Forecast!AA6</f>
         <v/>
       </c>
-      <c r="AB5" s="35">
+      <c r="AB5" s="37">
         <f>Forecast!AB6</f>
         <v/>
       </c>
-      <c r="AC5" s="35">
+      <c r="AC5" s="37">
         <f>Forecast!AC6</f>
         <v/>
       </c>
-      <c r="AD5" s="35">
+      <c r="AD5" s="37">
         <f>Forecast!AD6</f>
         <v/>
       </c>
-      <c r="AE5" s="35">
+      <c r="AE5" s="37">
         <f>Forecast!AE6</f>
         <v/>
       </c>
-      <c r="AF5" s="35">
+      <c r="AF5" s="37">
         <f>Forecast!AF6</f>
         <v/>
       </c>
-      <c r="AG5" s="35">
+      <c r="AG5" s="37">
         <f>Forecast!AG6</f>
         <v/>
       </c>
-      <c r="AH5" s="35">
+      <c r="AH5" s="37">
         <f>Forecast!AH6</f>
         <v/>
       </c>
-      <c r="AI5" s="35">
+      <c r="AI5" s="37">
         <f>Forecast!AI6</f>
         <v/>
       </c>
-      <c r="AJ5" s="35">
+      <c r="AJ5" s="37">
         <f>Forecast!AJ6</f>
         <v/>
       </c>
-      <c r="AK5" s="35">
+      <c r="AK5" s="37">
         <f>Forecast!AK6</f>
         <v/>
       </c>
-      <c r="AL5" s="35">
+      <c r="AL5" s="37">
         <f>Forecast!AL6</f>
         <v/>
       </c>
-      <c r="AM5" s="35">
+      <c r="AM5" s="37">
         <f>Forecast!AM6</f>
         <v/>
       </c>
@@ -6239,7 +6440,7 @@
         <f>Inputs!A94</f>
         <v/>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="37">
         <f>Inputs!D94</f>
         <v/>
       </c>
@@ -6393,7 +6594,7 @@
         <f>Inputs!A95</f>
         <v/>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="37">
         <f>Inputs!D95</f>
         <v/>
       </c>
@@ -6547,7 +6748,7 @@
         <f>Inputs!A96</f>
         <v/>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>Inputs!D96</f>
         <v/>
       </c>
@@ -6701,7 +6902,7 @@
         <f>Inputs!A97</f>
         <v/>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Inputs!D97</f>
         <v/>
       </c>
@@ -6855,7 +7056,7 @@
         <f>Inputs!A98</f>
         <v/>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>Inputs!D98</f>
         <v/>
       </c>
@@ -7009,7 +7210,7 @@
         <f>Inputs!A99</f>
         <v/>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="37">
         <f>Inputs!D99</f>
         <v/>
       </c>
@@ -7163,7 +7364,7 @@
         <f>Inputs!A100</f>
         <v/>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>Inputs!D100</f>
         <v/>
       </c>
@@ -7317,7 +7518,7 @@
         <f>Inputs!A101</f>
         <v/>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>Inputs!D101</f>
         <v/>
       </c>
@@ -7471,7 +7672,7 @@
         <f>Inputs!A102</f>
         <v/>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Inputs!D102</f>
         <v/>
       </c>
@@ -7625,7 +7826,7 @@
         <f>Inputs!A103</f>
         <v/>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="37">
         <f>Inputs!D103</f>
         <v/>
       </c>
@@ -7779,7 +7980,7 @@
         <f>Inputs!A104</f>
         <v/>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="37">
         <f>Inputs!D104</f>
         <v/>
       </c>
@@ -7933,7 +8134,7 @@
         <f>Inputs!A105</f>
         <v/>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="37">
         <f>Inputs!D105</f>
         <v/>
       </c>
@@ -8652,17 +8853,17 @@
           <t>M36</t>
         </is>
       </c>
-      <c r="AO4" s="36" t="inlineStr">
+      <c r="AO4" s="38" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="AP4" s="36" t="inlineStr">
+      <c r="AP4" s="38" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="AQ4" s="36" t="inlineStr">
+      <c r="AQ4" s="38" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
@@ -8728,150 +8929,150 @@
           <t>#</t>
         </is>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="37">
         <f>C6+1</f>
         <v/>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="37">
         <f>D6+1</f>
         <v/>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="37">
         <f>E6+1</f>
         <v/>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="37">
         <f>F6+1</f>
         <v/>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="37">
         <f>G6+1</f>
         <v/>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="37">
         <f>H6+1</f>
         <v/>
       </c>
-      <c r="J6" s="35">
+      <c r="J6" s="37">
         <f>I6+1</f>
         <v/>
       </c>
-      <c r="K6" s="35">
+      <c r="K6" s="37">
         <f>J6+1</f>
         <v/>
       </c>
-      <c r="L6" s="35">
+      <c r="L6" s="37">
         <f>K6+1</f>
         <v/>
       </c>
-      <c r="M6" s="35">
+      <c r="M6" s="37">
         <f>L6+1</f>
         <v/>
       </c>
-      <c r="N6" s="35">
+      <c r="N6" s="37">
         <f>M6+1</f>
         <v/>
       </c>
-      <c r="O6" s="35">
+      <c r="O6" s="37">
         <f>N6+1</f>
         <v/>
       </c>
-      <c r="P6" s="35">
+      <c r="P6" s="37">
         <f>O6+1</f>
         <v/>
       </c>
-      <c r="Q6" s="35">
+      <c r="Q6" s="37">
         <f>P6+1</f>
         <v/>
       </c>
-      <c r="R6" s="35">
+      <c r="R6" s="37">
         <f>Q6+1</f>
         <v/>
       </c>
-      <c r="S6" s="35">
+      <c r="S6" s="37">
         <f>R6+1</f>
         <v/>
       </c>
-      <c r="T6" s="35">
+      <c r="T6" s="37">
         <f>S6+1</f>
         <v/>
       </c>
-      <c r="U6" s="35">
+      <c r="U6" s="37">
         <f>T6+1</f>
         <v/>
       </c>
-      <c r="V6" s="35">
+      <c r="V6" s="37">
         <f>U6+1</f>
         <v/>
       </c>
-      <c r="W6" s="35">
+      <c r="W6" s="37">
         <f>V6+1</f>
         <v/>
       </c>
-      <c r="X6" s="35">
+      <c r="X6" s="37">
         <f>W6+1</f>
         <v/>
       </c>
-      <c r="Y6" s="35">
+      <c r="Y6" s="37">
         <f>X6+1</f>
         <v/>
       </c>
-      <c r="Z6" s="35">
+      <c r="Z6" s="37">
         <f>Y6+1</f>
         <v/>
       </c>
-      <c r="AA6" s="35">
+      <c r="AA6" s="37">
         <f>Z6+1</f>
         <v/>
       </c>
-      <c r="AB6" s="35">
+      <c r="AB6" s="37">
         <f>AA6+1</f>
         <v/>
       </c>
-      <c r="AC6" s="35">
+      <c r="AC6" s="37">
         <f>AB6+1</f>
         <v/>
       </c>
-      <c r="AD6" s="35">
+      <c r="AD6" s="37">
         <f>AC6+1</f>
         <v/>
       </c>
-      <c r="AE6" s="35">
+      <c r="AE6" s="37">
         <f>AD6+1</f>
         <v/>
       </c>
-      <c r="AF6" s="35">
+      <c r="AF6" s="37">
         <f>AE6+1</f>
         <v/>
       </c>
-      <c r="AG6" s="35">
+      <c r="AG6" s="37">
         <f>AF6+1</f>
         <v/>
       </c>
-      <c r="AH6" s="35">
+      <c r="AH6" s="37">
         <f>AG6+1</f>
         <v/>
       </c>
-      <c r="AI6" s="35">
+      <c r="AI6" s="37">
         <f>AH6+1</f>
         <v/>
       </c>
-      <c r="AJ6" s="35">
+      <c r="AJ6" s="37">
         <f>AI6+1</f>
         <v/>
       </c>
-      <c r="AK6" s="35">
+      <c r="AK6" s="37">
         <f>AJ6+1</f>
         <v/>
       </c>
-      <c r="AL6" s="35">
+      <c r="AL6" s="37">
         <f>AK6+1</f>
         <v/>
       </c>
-      <c r="AM6" s="35">
+      <c r="AM6" s="37">
         <f>AL6+1</f>
         <v/>
       </c>
@@ -8887,147 +9088,147 @@
           <t>date</t>
         </is>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="39">
         <f>EDATE(Inputs!$B$7,D6-1)</f>
         <v/>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="39">
         <f>EDATE(Inputs!$B$7,E6-1)</f>
         <v/>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="39">
         <f>EDATE(Inputs!$B$7,F6-1)</f>
         <v/>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="39">
         <f>EDATE(Inputs!$B$7,G6-1)</f>
         <v/>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="39">
         <f>EDATE(Inputs!$B$7,H6-1)</f>
         <v/>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="39">
         <f>EDATE(Inputs!$B$7,I6-1)</f>
         <v/>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="39">
         <f>EDATE(Inputs!$B$7,J6-1)</f>
         <v/>
       </c>
-      <c r="K7" s="37">
+      <c r="K7" s="39">
         <f>EDATE(Inputs!$B$7,K6-1)</f>
         <v/>
       </c>
-      <c r="L7" s="37">
+      <c r="L7" s="39">
         <f>EDATE(Inputs!$B$7,L6-1)</f>
         <v/>
       </c>
-      <c r="M7" s="37">
+      <c r="M7" s="39">
         <f>EDATE(Inputs!$B$7,M6-1)</f>
         <v/>
       </c>
-      <c r="N7" s="37">
+      <c r="N7" s="39">
         <f>EDATE(Inputs!$B$7,N6-1)</f>
         <v/>
       </c>
-      <c r="O7" s="37">
+      <c r="O7" s="39">
         <f>EDATE(Inputs!$B$7,O6-1)</f>
         <v/>
       </c>
-      <c r="P7" s="37">
+      <c r="P7" s="39">
         <f>EDATE(Inputs!$B$7,P6-1)</f>
         <v/>
       </c>
-      <c r="Q7" s="37">
+      <c r="Q7" s="39">
         <f>EDATE(Inputs!$B$7,Q6-1)</f>
         <v/>
       </c>
-      <c r="R7" s="37">
+      <c r="R7" s="39">
         <f>EDATE(Inputs!$B$7,R6-1)</f>
         <v/>
       </c>
-      <c r="S7" s="37">
+      <c r="S7" s="39">
         <f>EDATE(Inputs!$B$7,S6-1)</f>
         <v/>
       </c>
-      <c r="T7" s="37">
+      <c r="T7" s="39">
         <f>EDATE(Inputs!$B$7,T6-1)</f>
         <v/>
       </c>
-      <c r="U7" s="37">
+      <c r="U7" s="39">
         <f>EDATE(Inputs!$B$7,U6-1)</f>
         <v/>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="39">
         <f>EDATE(Inputs!$B$7,V6-1)</f>
         <v/>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="39">
         <f>EDATE(Inputs!$B$7,W6-1)</f>
         <v/>
       </c>
-      <c r="X7" s="37">
+      <c r="X7" s="39">
         <f>EDATE(Inputs!$B$7,X6-1)</f>
         <v/>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="39">
         <f>EDATE(Inputs!$B$7,Y6-1)</f>
         <v/>
       </c>
-      <c r="Z7" s="37">
+      <c r="Z7" s="39">
         <f>EDATE(Inputs!$B$7,Z6-1)</f>
         <v/>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="39">
         <f>EDATE(Inputs!$B$7,AA6-1)</f>
         <v/>
       </c>
-      <c r="AB7" s="37">
+      <c r="AB7" s="39">
         <f>EDATE(Inputs!$B$7,AB6-1)</f>
         <v/>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="39">
         <f>EDATE(Inputs!$B$7,AC6-1)</f>
         <v/>
       </c>
-      <c r="AD7" s="37">
+      <c r="AD7" s="39">
         <f>EDATE(Inputs!$B$7,AD6-1)</f>
         <v/>
       </c>
-      <c r="AE7" s="37">
+      <c r="AE7" s="39">
         <f>EDATE(Inputs!$B$7,AE6-1)</f>
         <v/>
       </c>
-      <c r="AF7" s="37">
+      <c r="AF7" s="39">
         <f>EDATE(Inputs!$B$7,AF6-1)</f>
         <v/>
       </c>
-      <c r="AG7" s="37">
+      <c r="AG7" s="39">
         <f>EDATE(Inputs!$B$7,AG6-1)</f>
         <v/>
       </c>
-      <c r="AH7" s="37">
+      <c r="AH7" s="39">
         <f>EDATE(Inputs!$B$7,AH6-1)</f>
         <v/>
       </c>
-      <c r="AI7" s="37">
+      <c r="AI7" s="39">
         <f>EDATE(Inputs!$B$7,AI6-1)</f>
         <v/>
       </c>
-      <c r="AJ7" s="37">
+      <c r="AJ7" s="39">
         <f>EDATE(Inputs!$B$7,AJ6-1)</f>
         <v/>
       </c>
-      <c r="AK7" s="37">
+      <c r="AK7" s="39">
         <f>EDATE(Inputs!$B$7,AK6-1)</f>
         <v/>
       </c>
-      <c r="AL7" s="37">
+      <c r="AL7" s="39">
         <f>EDATE(Inputs!$B$7,AL6-1)</f>
         <v/>
       </c>
-      <c r="AM7" s="37">
+      <c r="AM7" s="39">
         <f>EDATE(Inputs!$B$7,AM6-1)</f>
         <v/>
       </c>
@@ -9043,147 +9244,147 @@
           <t>1-12</t>
         </is>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="37">
         <f>MONTH(D7)</f>
         <v/>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="37">
         <f>MONTH(E7)</f>
         <v/>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="37">
         <f>MONTH(F7)</f>
         <v/>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="37">
         <f>MONTH(G7)</f>
         <v/>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="37">
         <f>MONTH(H7)</f>
         <v/>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="37">
         <f>MONTH(I7)</f>
         <v/>
       </c>
-      <c r="J8" s="35">
+      <c r="J8" s="37">
         <f>MONTH(J7)</f>
         <v/>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="37">
         <f>MONTH(K7)</f>
         <v/>
       </c>
-      <c r="L8" s="35">
+      <c r="L8" s="37">
         <f>MONTH(L7)</f>
         <v/>
       </c>
-      <c r="M8" s="35">
+      <c r="M8" s="37">
         <f>MONTH(M7)</f>
         <v/>
       </c>
-      <c r="N8" s="35">
+      <c r="N8" s="37">
         <f>MONTH(N7)</f>
         <v/>
       </c>
-      <c r="O8" s="35">
+      <c r="O8" s="37">
         <f>MONTH(O7)</f>
         <v/>
       </c>
-      <c r="P8" s="35">
+      <c r="P8" s="37">
         <f>MONTH(P7)</f>
         <v/>
       </c>
-      <c r="Q8" s="35">
+      <c r="Q8" s="37">
         <f>MONTH(Q7)</f>
         <v/>
       </c>
-      <c r="R8" s="35">
+      <c r="R8" s="37">
         <f>MONTH(R7)</f>
         <v/>
       </c>
-      <c r="S8" s="35">
+      <c r="S8" s="37">
         <f>MONTH(S7)</f>
         <v/>
       </c>
-      <c r="T8" s="35">
+      <c r="T8" s="37">
         <f>MONTH(T7)</f>
         <v/>
       </c>
-      <c r="U8" s="35">
+      <c r="U8" s="37">
         <f>MONTH(U7)</f>
         <v/>
       </c>
-      <c r="V8" s="35">
+      <c r="V8" s="37">
         <f>MONTH(V7)</f>
         <v/>
       </c>
-      <c r="W8" s="35">
+      <c r="W8" s="37">
         <f>MONTH(W7)</f>
         <v/>
       </c>
-      <c r="X8" s="35">
+      <c r="X8" s="37">
         <f>MONTH(X7)</f>
         <v/>
       </c>
-      <c r="Y8" s="35">
+      <c r="Y8" s="37">
         <f>MONTH(Y7)</f>
         <v/>
       </c>
-      <c r="Z8" s="35">
+      <c r="Z8" s="37">
         <f>MONTH(Z7)</f>
         <v/>
       </c>
-      <c r="AA8" s="35">
+      <c r="AA8" s="37">
         <f>MONTH(AA7)</f>
         <v/>
       </c>
-      <c r="AB8" s="35">
+      <c r="AB8" s="37">
         <f>MONTH(AB7)</f>
         <v/>
       </c>
-      <c r="AC8" s="35">
+      <c r="AC8" s="37">
         <f>MONTH(AC7)</f>
         <v/>
       </c>
-      <c r="AD8" s="35">
+      <c r="AD8" s="37">
         <f>MONTH(AD7)</f>
         <v/>
       </c>
-      <c r="AE8" s="35">
+      <c r="AE8" s="37">
         <f>MONTH(AE7)</f>
         <v/>
       </c>
-      <c r="AF8" s="35">
+      <c r="AF8" s="37">
         <f>MONTH(AF7)</f>
         <v/>
       </c>
-      <c r="AG8" s="35">
+      <c r="AG8" s="37">
         <f>MONTH(AG7)</f>
         <v/>
       </c>
-      <c r="AH8" s="35">
+      <c r="AH8" s="37">
         <f>MONTH(AH7)</f>
         <v/>
       </c>
-      <c r="AI8" s="35">
+      <c r="AI8" s="37">
         <f>MONTH(AI7)</f>
         <v/>
       </c>
-      <c r="AJ8" s="35">
+      <c r="AJ8" s="37">
         <f>MONTH(AJ7)</f>
         <v/>
       </c>
-      <c r="AK8" s="35">
+      <c r="AK8" s="37">
         <f>MONTH(AK7)</f>
         <v/>
       </c>
-      <c r="AL8" s="35">
+      <c r="AL8" s="37">
         <f>MONTH(AL7)</f>
         <v/>
       </c>
-      <c r="AM8" s="35">
+      <c r="AM8" s="37">
         <f>MONTH(AM7)</f>
         <v/>
       </c>
@@ -10802,159 +11003,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="37">
         <f>IFERROR(D13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="37">
         <f>IFERROR(E13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="37">
         <f>IFERROR(F13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="37">
         <f>IFERROR(G13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="37">
         <f>IFERROR(H13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="37">
         <f>IFERROR(I13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="37">
         <f>IFERROR(J13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="K20" s="35">
+      <c r="K20" s="37">
         <f>IFERROR(K13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="L20" s="35">
+      <c r="L20" s="37">
         <f>IFERROR(L13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="M20" s="35">
+      <c r="M20" s="37">
         <f>IFERROR(M13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="N20" s="35">
+      <c r="N20" s="37">
         <f>IFERROR(N13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="O20" s="35">
+      <c r="O20" s="37">
         <f>IFERROR(O13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="P20" s="35">
+      <c r="P20" s="37">
         <f>IFERROR(P13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="Q20" s="35">
+      <c r="Q20" s="37">
         <f>IFERROR(Q13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="R20" s="35">
+      <c r="R20" s="37">
         <f>IFERROR(R13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="S20" s="35">
+      <c r="S20" s="37">
         <f>IFERROR(S13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="T20" s="35">
+      <c r="T20" s="37">
         <f>IFERROR(T13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="U20" s="35">
+      <c r="U20" s="37">
         <f>IFERROR(U13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="V20" s="35">
+      <c r="V20" s="37">
         <f>IFERROR(V13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="W20" s="35">
+      <c r="W20" s="37">
         <f>IFERROR(W13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="X20" s="35">
+      <c r="X20" s="37">
         <f>IFERROR(X13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="Y20" s="35">
+      <c r="Y20" s="37">
         <f>IFERROR(Y13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="Z20" s="35">
+      <c r="Z20" s="37">
         <f>IFERROR(Z13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AA20" s="35">
+      <c r="AA20" s="37">
         <f>IFERROR(AA13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AB20" s="35">
+      <c r="AB20" s="37">
         <f>IFERROR(AB13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AC20" s="35">
+      <c r="AC20" s="37">
         <f>IFERROR(AC13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AD20" s="35">
+      <c r="AD20" s="37">
         <f>IFERROR(AD13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AE20" s="35">
+      <c r="AE20" s="37">
         <f>IFERROR(AE13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AF20" s="35">
+      <c r="AF20" s="37">
         <f>IFERROR(AF13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AG20" s="35">
+      <c r="AG20" s="37">
         <f>IFERROR(AG13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AH20" s="35">
+      <c r="AH20" s="37">
         <f>IFERROR(AH13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AI20" s="35">
+      <c r="AI20" s="37">
         <f>IFERROR(AI13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AJ20" s="35">
+      <c r="AJ20" s="37">
         <f>IFERROR(AJ13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AK20" s="35">
+      <c r="AK20" s="37">
         <f>IFERROR(AK13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AL20" s="35">
+      <c r="AL20" s="37">
         <f>IFERROR(AL13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AM20" s="35">
+      <c r="AM20" s="37">
         <f>IFERROR(AM13/'Unit Economics'!$C$15,0)</f>
         <v/>
       </c>
-      <c r="AO20" s="35">
+      <c r="AO20" s="37">
         <f>SUM(D20:O20)</f>
         <v/>
       </c>
-      <c r="AP20" s="35">
+      <c r="AP20" s="37">
         <f>SUM(P20:AA20)</f>
         <v/>
       </c>
-      <c r="AQ20" s="35">
+      <c r="AQ20" s="37">
         <f>SUM(AB20:AM20)</f>
         <v/>
       </c>
@@ -10969,159 +11170,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="37">
         <f>IFERROR(D14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="37">
         <f>IFERROR(E14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="37">
         <f>IFERROR(F14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="37">
         <f>IFERROR(G14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="37">
         <f>IFERROR(H14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="37">
         <f>IFERROR(I14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="37">
         <f>IFERROR(J14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="K21" s="35">
+      <c r="K21" s="37">
         <f>IFERROR(K14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="L21" s="35">
+      <c r="L21" s="37">
         <f>IFERROR(L14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="M21" s="35">
+      <c r="M21" s="37">
         <f>IFERROR(M14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="N21" s="35">
+      <c r="N21" s="37">
         <f>IFERROR(N14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="O21" s="35">
+      <c r="O21" s="37">
         <f>IFERROR(O14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="P21" s="35">
+      <c r="P21" s="37">
         <f>IFERROR(P14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="Q21" s="35">
+      <c r="Q21" s="37">
         <f>IFERROR(Q14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="R21" s="35">
+      <c r="R21" s="37">
         <f>IFERROR(R14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="S21" s="35">
+      <c r="S21" s="37">
         <f>IFERROR(S14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="T21" s="35">
+      <c r="T21" s="37">
         <f>IFERROR(T14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="U21" s="35">
+      <c r="U21" s="37">
         <f>IFERROR(U14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="V21" s="35">
+      <c r="V21" s="37">
         <f>IFERROR(V14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="W21" s="35">
+      <c r="W21" s="37">
         <f>IFERROR(W14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="X21" s="35">
+      <c r="X21" s="37">
         <f>IFERROR(X14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="Y21" s="35">
+      <c r="Y21" s="37">
         <f>IFERROR(Y14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="Z21" s="35">
+      <c r="Z21" s="37">
         <f>IFERROR(Z14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AA21" s="35">
+      <c r="AA21" s="37">
         <f>IFERROR(AA14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AB21" s="35">
+      <c r="AB21" s="37">
         <f>IFERROR(AB14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AC21" s="35">
+      <c r="AC21" s="37">
         <f>IFERROR(AC14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AD21" s="35">
+      <c r="AD21" s="37">
         <f>IFERROR(AD14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AE21" s="35">
+      <c r="AE21" s="37">
         <f>IFERROR(AE14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AF21" s="35">
+      <c r="AF21" s="37">
         <f>IFERROR(AF14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AG21" s="35">
+      <c r="AG21" s="37">
         <f>IFERROR(AG14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AH21" s="35">
+      <c r="AH21" s="37">
         <f>IFERROR(AH14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AI21" s="35">
+      <c r="AI21" s="37">
         <f>IFERROR(AI14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AJ21" s="35">
+      <c r="AJ21" s="37">
         <f>IFERROR(AJ14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AK21" s="35">
+      <c r="AK21" s="37">
         <f>IFERROR(AK14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AL21" s="35">
+      <c r="AL21" s="37">
         <f>IFERROR(AL14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AM21" s="35">
+      <c r="AM21" s="37">
         <f>IFERROR(AM14/'Unit Economics'!$C$16,0)</f>
         <v/>
       </c>
-      <c r="AO21" s="35">
+      <c r="AO21" s="37">
         <f>SUM(D21:O21)</f>
         <v/>
       </c>
-      <c r="AP21" s="35">
+      <c r="AP21" s="37">
         <f>SUM(P21:AA21)</f>
         <v/>
       </c>
-      <c r="AQ21" s="35">
+      <c r="AQ21" s="37">
         <f>SUM(AB21:AM21)</f>
         <v/>
       </c>
@@ -11136,159 +11337,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="37">
         <f>IFERROR(D15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="37">
         <f>IFERROR(E15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="37">
         <f>IFERROR(F15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="37">
         <f>IFERROR(G15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="37">
         <f>IFERROR(H15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="I22" s="35">
+      <c r="I22" s="37">
         <f>IFERROR(I15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="37">
         <f>IFERROR(J15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="K22" s="35">
+      <c r="K22" s="37">
         <f>IFERROR(K15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="L22" s="35">
+      <c r="L22" s="37">
         <f>IFERROR(L15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="M22" s="35">
+      <c r="M22" s="37">
         <f>IFERROR(M15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="N22" s="35">
+      <c r="N22" s="37">
         <f>IFERROR(N15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="O22" s="35">
+      <c r="O22" s="37">
         <f>IFERROR(O15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="P22" s="35">
+      <c r="P22" s="37">
         <f>IFERROR(P15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="Q22" s="35">
+      <c r="Q22" s="37">
         <f>IFERROR(Q15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="R22" s="35">
+      <c r="R22" s="37">
         <f>IFERROR(R15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="S22" s="35">
+      <c r="S22" s="37">
         <f>IFERROR(S15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="T22" s="35">
+      <c r="T22" s="37">
         <f>IFERROR(T15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="U22" s="35">
+      <c r="U22" s="37">
         <f>IFERROR(U15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="V22" s="35">
+      <c r="V22" s="37">
         <f>IFERROR(V15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="W22" s="35">
+      <c r="W22" s="37">
         <f>IFERROR(W15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="X22" s="35">
+      <c r="X22" s="37">
         <f>IFERROR(X15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="Y22" s="35">
+      <c r="Y22" s="37">
         <f>IFERROR(Y15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="Z22" s="35">
+      <c r="Z22" s="37">
         <f>IFERROR(Z15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AA22" s="35">
+      <c r="AA22" s="37">
         <f>IFERROR(AA15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AB22" s="35">
+      <c r="AB22" s="37">
         <f>IFERROR(AB15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AC22" s="35">
+      <c r="AC22" s="37">
         <f>IFERROR(AC15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AD22" s="35">
+      <c r="AD22" s="37">
         <f>IFERROR(AD15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AE22" s="35">
+      <c r="AE22" s="37">
         <f>IFERROR(AE15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AF22" s="35">
+      <c r="AF22" s="37">
         <f>IFERROR(AF15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AG22" s="35">
+      <c r="AG22" s="37">
         <f>IFERROR(AG15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AH22" s="35">
+      <c r="AH22" s="37">
         <f>IFERROR(AH15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AI22" s="35">
+      <c r="AI22" s="37">
         <f>IFERROR(AI15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AJ22" s="35">
+      <c r="AJ22" s="37">
         <f>IFERROR(AJ15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AK22" s="35">
+      <c r="AK22" s="37">
         <f>IFERROR(AK15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AL22" s="35">
+      <c r="AL22" s="37">
         <f>IFERROR(AL15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AM22" s="35">
+      <c r="AM22" s="37">
         <f>IFERROR(AM15/'Unit Economics'!$C$17,0)</f>
         <v/>
       </c>
-      <c r="AO22" s="35">
+      <c r="AO22" s="37">
         <f>SUM(D22:O22)</f>
         <v/>
       </c>
-      <c r="AP22" s="35">
+      <c r="AP22" s="37">
         <f>SUM(P22:AA22)</f>
         <v/>
       </c>
-      <c r="AQ22" s="35">
+      <c r="AQ22" s="37">
         <f>SUM(AB22:AM22)</f>
         <v/>
       </c>
@@ -11303,159 +11504,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="37">
         <f>IFERROR(D16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="37">
         <f>IFERROR(E16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="37">
         <f>IFERROR(F16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="37">
         <f>IFERROR(G16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="37">
         <f>IFERROR(H16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="37">
         <f>IFERROR(I16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="37">
         <f>IFERROR(J16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="K23" s="35">
+      <c r="K23" s="37">
         <f>IFERROR(K16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="L23" s="35">
+      <c r="L23" s="37">
         <f>IFERROR(L16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="M23" s="35">
+      <c r="M23" s="37">
         <f>IFERROR(M16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="N23" s="35">
+      <c r="N23" s="37">
         <f>IFERROR(N16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="O23" s="35">
+      <c r="O23" s="37">
         <f>IFERROR(O16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="P23" s="35">
+      <c r="P23" s="37">
         <f>IFERROR(P16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="Q23" s="35">
+      <c r="Q23" s="37">
         <f>IFERROR(Q16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="R23" s="35">
+      <c r="R23" s="37">
         <f>IFERROR(R16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="S23" s="35">
+      <c r="S23" s="37">
         <f>IFERROR(S16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="T23" s="35">
+      <c r="T23" s="37">
         <f>IFERROR(T16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="U23" s="35">
+      <c r="U23" s="37">
         <f>IFERROR(U16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="V23" s="35">
+      <c r="V23" s="37">
         <f>IFERROR(V16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="W23" s="35">
+      <c r="W23" s="37">
         <f>IFERROR(W16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="X23" s="35">
+      <c r="X23" s="37">
         <f>IFERROR(X16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="Y23" s="35">
+      <c r="Y23" s="37">
         <f>IFERROR(Y16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="Z23" s="35">
+      <c r="Z23" s="37">
         <f>IFERROR(Z16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AA23" s="35">
+      <c r="AA23" s="37">
         <f>IFERROR(AA16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AB23" s="35">
+      <c r="AB23" s="37">
         <f>IFERROR(AB16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AC23" s="35">
+      <c r="AC23" s="37">
         <f>IFERROR(AC16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AD23" s="35">
+      <c r="AD23" s="37">
         <f>IFERROR(AD16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AE23" s="35">
+      <c r="AE23" s="37">
         <f>IFERROR(AE16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AF23" s="35">
+      <c r="AF23" s="37">
         <f>IFERROR(AF16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AG23" s="35">
+      <c r="AG23" s="37">
         <f>IFERROR(AG16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AH23" s="35">
+      <c r="AH23" s="37">
         <f>IFERROR(AH16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AI23" s="35">
+      <c r="AI23" s="37">
         <f>IFERROR(AI16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AJ23" s="35">
+      <c r="AJ23" s="37">
         <f>IFERROR(AJ16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AK23" s="35">
+      <c r="AK23" s="37">
         <f>IFERROR(AK16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AL23" s="35">
+      <c r="AL23" s="37">
         <f>IFERROR(AL16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AM23" s="35">
+      <c r="AM23" s="37">
         <f>IFERROR(AM16/'Unit Economics'!$C$18,0)</f>
         <v/>
       </c>
-      <c r="AO23" s="35">
+      <c r="AO23" s="37">
         <f>SUM(D23:O23)</f>
         <v/>
       </c>
-      <c r="AP23" s="35">
+      <c r="AP23" s="37">
         <f>SUM(P23:AA23)</f>
         <v/>
       </c>
-      <c r="AQ23" s="35">
+      <c r="AQ23" s="37">
         <f>SUM(AB23:AM23)</f>
         <v/>
       </c>
@@ -11470,159 +11671,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="37">
         <f>IFERROR(D17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="37">
         <f>IFERROR(E17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="37">
         <f>IFERROR(F17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="37">
         <f>IFERROR(G17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="37">
         <f>IFERROR(H17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="37">
         <f>IFERROR(I17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="37">
         <f>IFERROR(J17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="K24" s="35">
+      <c r="K24" s="37">
         <f>IFERROR(K17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="L24" s="35">
+      <c r="L24" s="37">
         <f>IFERROR(L17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="M24" s="35">
+      <c r="M24" s="37">
         <f>IFERROR(M17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="N24" s="35">
+      <c r="N24" s="37">
         <f>IFERROR(N17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="O24" s="35">
+      <c r="O24" s="37">
         <f>IFERROR(O17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="P24" s="35">
+      <c r="P24" s="37">
         <f>IFERROR(P17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="Q24" s="35">
+      <c r="Q24" s="37">
         <f>IFERROR(Q17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="R24" s="35">
+      <c r="R24" s="37">
         <f>IFERROR(R17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="S24" s="35">
+      <c r="S24" s="37">
         <f>IFERROR(S17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="T24" s="35">
+      <c r="T24" s="37">
         <f>IFERROR(T17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="U24" s="35">
+      <c r="U24" s="37">
         <f>IFERROR(U17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="V24" s="35">
+      <c r="V24" s="37">
         <f>IFERROR(V17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="W24" s="35">
+      <c r="W24" s="37">
         <f>IFERROR(W17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="X24" s="35">
+      <c r="X24" s="37">
         <f>IFERROR(X17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="Y24" s="35">
+      <c r="Y24" s="37">
         <f>IFERROR(Y17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="Z24" s="35">
+      <c r="Z24" s="37">
         <f>IFERROR(Z17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AA24" s="35">
+      <c r="AA24" s="37">
         <f>IFERROR(AA17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AB24" s="35">
+      <c r="AB24" s="37">
         <f>IFERROR(AB17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AC24" s="35">
+      <c r="AC24" s="37">
         <f>IFERROR(AC17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AD24" s="35">
+      <c r="AD24" s="37">
         <f>IFERROR(AD17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AE24" s="35">
+      <c r="AE24" s="37">
         <f>IFERROR(AE17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AF24" s="35">
+      <c r="AF24" s="37">
         <f>IFERROR(AF17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AG24" s="35">
+      <c r="AG24" s="37">
         <f>IFERROR(AG17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AH24" s="35">
+      <c r="AH24" s="37">
         <f>IFERROR(AH17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AI24" s="35">
+      <c r="AI24" s="37">
         <f>IFERROR(AI17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AJ24" s="35">
+      <c r="AJ24" s="37">
         <f>IFERROR(AJ17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AK24" s="35">
+      <c r="AK24" s="37">
         <f>IFERROR(AK17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AL24" s="35">
+      <c r="AL24" s="37">
         <f>IFERROR(AL17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AM24" s="35">
+      <c r="AM24" s="37">
         <f>IFERROR(AM17/'Unit Economics'!$C$19,0)</f>
         <v/>
       </c>
-      <c r="AO24" s="35">
+      <c r="AO24" s="37">
         <f>SUM(D24:O24)</f>
         <v/>
       </c>
-      <c r="AP24" s="35">
+      <c r="AP24" s="37">
         <f>SUM(P24:AA24)</f>
         <v/>
       </c>
-      <c r="AQ24" s="35">
+      <c r="AQ24" s="37">
         <f>SUM(AB24:AM24)</f>
         <v/>
       </c>
@@ -11637,159 +11838,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="37">
         <f>IFERROR(D18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="37">
         <f>IFERROR(E18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="37">
         <f>IFERROR(F18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="37">
         <f>IFERROR(G18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="37">
         <f>IFERROR(H18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="I25" s="35">
+      <c r="I25" s="37">
         <f>IFERROR(I18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="37">
         <f>IFERROR(J18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="K25" s="35">
+      <c r="K25" s="37">
         <f>IFERROR(K18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="L25" s="35">
+      <c r="L25" s="37">
         <f>IFERROR(L18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="M25" s="35">
+      <c r="M25" s="37">
         <f>IFERROR(M18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="N25" s="35">
+      <c r="N25" s="37">
         <f>IFERROR(N18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="O25" s="35">
+      <c r="O25" s="37">
         <f>IFERROR(O18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="P25" s="35">
+      <c r="P25" s="37">
         <f>IFERROR(P18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="Q25" s="35">
+      <c r="Q25" s="37">
         <f>IFERROR(Q18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="R25" s="35">
+      <c r="R25" s="37">
         <f>IFERROR(R18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="S25" s="35">
+      <c r="S25" s="37">
         <f>IFERROR(S18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="T25" s="35">
+      <c r="T25" s="37">
         <f>IFERROR(T18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="U25" s="35">
+      <c r="U25" s="37">
         <f>IFERROR(U18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="V25" s="35">
+      <c r="V25" s="37">
         <f>IFERROR(V18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="W25" s="35">
+      <c r="W25" s="37">
         <f>IFERROR(W18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="X25" s="35">
+      <c r="X25" s="37">
         <f>IFERROR(X18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="Y25" s="35">
+      <c r="Y25" s="37">
         <f>IFERROR(Y18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="Z25" s="35">
+      <c r="Z25" s="37">
         <f>IFERROR(Z18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AA25" s="35">
+      <c r="AA25" s="37">
         <f>IFERROR(AA18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AB25" s="35">
+      <c r="AB25" s="37">
         <f>IFERROR(AB18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AC25" s="35">
+      <c r="AC25" s="37">
         <f>IFERROR(AC18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AD25" s="35">
+      <c r="AD25" s="37">
         <f>IFERROR(AD18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AE25" s="35">
+      <c r="AE25" s="37">
         <f>IFERROR(AE18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AF25" s="35">
+      <c r="AF25" s="37">
         <f>IFERROR(AF18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AG25" s="35">
+      <c r="AG25" s="37">
         <f>IFERROR(AG18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AH25" s="35">
+      <c r="AH25" s="37">
         <f>IFERROR(AH18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AI25" s="35">
+      <c r="AI25" s="37">
         <f>IFERROR(AI18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AJ25" s="35">
+      <c r="AJ25" s="37">
         <f>IFERROR(AJ18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AK25" s="35">
+      <c r="AK25" s="37">
         <f>IFERROR(AK18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AL25" s="35">
+      <c r="AL25" s="37">
         <f>IFERROR(AL18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AM25" s="35">
+      <c r="AM25" s="37">
         <f>IFERROR(AM18/'Unit Economics'!$C$20,0)</f>
         <v/>
       </c>
-      <c r="AO25" s="35">
+      <c r="AO25" s="37">
         <f>SUM(D25:O25)</f>
         <v/>
       </c>
-      <c r="AP25" s="35">
+      <c r="AP25" s="37">
         <f>SUM(P25:AA25)</f>
         <v/>
       </c>
-      <c r="AQ25" s="35">
+      <c r="AQ25" s="37">
         <f>SUM(AB25:AM25)</f>
         <v/>
       </c>
@@ -11805,159 +12006,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="40">
         <f>SUM(D20:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="40">
         <f>SUM(E20:E25)</f>
         <v/>
       </c>
-      <c r="F26" s="38">
+      <c r="F26" s="40">
         <f>SUM(F20:F25)</f>
         <v/>
       </c>
-      <c r="G26" s="38">
+      <c r="G26" s="40">
         <f>SUM(G20:G25)</f>
         <v/>
       </c>
-      <c r="H26" s="38">
+      <c r="H26" s="40">
         <f>SUM(H20:H25)</f>
         <v/>
       </c>
-      <c r="I26" s="38">
+      <c r="I26" s="40">
         <f>SUM(I20:I25)</f>
         <v/>
       </c>
-      <c r="J26" s="38">
+      <c r="J26" s="40">
         <f>SUM(J20:J25)</f>
         <v/>
       </c>
-      <c r="K26" s="38">
+      <c r="K26" s="40">
         <f>SUM(K20:K25)</f>
         <v/>
       </c>
-      <c r="L26" s="38">
+      <c r="L26" s="40">
         <f>SUM(L20:L25)</f>
         <v/>
       </c>
-      <c r="M26" s="38">
+      <c r="M26" s="40">
         <f>SUM(M20:M25)</f>
         <v/>
       </c>
-      <c r="N26" s="38">
+      <c r="N26" s="40">
         <f>SUM(N20:N25)</f>
         <v/>
       </c>
-      <c r="O26" s="38">
+      <c r="O26" s="40">
         <f>SUM(O20:O25)</f>
         <v/>
       </c>
-      <c r="P26" s="38">
+      <c r="P26" s="40">
         <f>SUM(P20:P25)</f>
         <v/>
       </c>
-      <c r="Q26" s="38">
+      <c r="Q26" s="40">
         <f>SUM(Q20:Q25)</f>
         <v/>
       </c>
-      <c r="R26" s="38">
+      <c r="R26" s="40">
         <f>SUM(R20:R25)</f>
         <v/>
       </c>
-      <c r="S26" s="38">
+      <c r="S26" s="40">
         <f>SUM(S20:S25)</f>
         <v/>
       </c>
-      <c r="T26" s="38">
+      <c r="T26" s="40">
         <f>SUM(T20:T25)</f>
         <v/>
       </c>
-      <c r="U26" s="38">
+      <c r="U26" s="40">
         <f>SUM(U20:U25)</f>
         <v/>
       </c>
-      <c r="V26" s="38">
+      <c r="V26" s="40">
         <f>SUM(V20:V25)</f>
         <v/>
       </c>
-      <c r="W26" s="38">
+      <c r="W26" s="40">
         <f>SUM(W20:W25)</f>
         <v/>
       </c>
-      <c r="X26" s="38">
+      <c r="X26" s="40">
         <f>SUM(X20:X25)</f>
         <v/>
       </c>
-      <c r="Y26" s="38">
+      <c r="Y26" s="40">
         <f>SUM(Y20:Y25)</f>
         <v/>
       </c>
-      <c r="Z26" s="38">
+      <c r="Z26" s="40">
         <f>SUM(Z20:Z25)</f>
         <v/>
       </c>
-      <c r="AA26" s="38">
+      <c r="AA26" s="40">
         <f>SUM(AA20:AA25)</f>
         <v/>
       </c>
-      <c r="AB26" s="38">
+      <c r="AB26" s="40">
         <f>SUM(AB20:AB25)</f>
         <v/>
       </c>
-      <c r="AC26" s="38">
+      <c r="AC26" s="40">
         <f>SUM(AC20:AC25)</f>
         <v/>
       </c>
-      <c r="AD26" s="38">
+      <c r="AD26" s="40">
         <f>SUM(AD20:AD25)</f>
         <v/>
       </c>
-      <c r="AE26" s="38">
+      <c r="AE26" s="40">
         <f>SUM(AE20:AE25)</f>
         <v/>
       </c>
-      <c r="AF26" s="38">
+      <c r="AF26" s="40">
         <f>SUM(AF20:AF25)</f>
         <v/>
       </c>
-      <c r="AG26" s="38">
+      <c r="AG26" s="40">
         <f>SUM(AG20:AG25)</f>
         <v/>
       </c>
-      <c r="AH26" s="38">
+      <c r="AH26" s="40">
         <f>SUM(AH20:AH25)</f>
         <v/>
       </c>
-      <c r="AI26" s="38">
+      <c r="AI26" s="40">
         <f>SUM(AI20:AI25)</f>
         <v/>
       </c>
-      <c r="AJ26" s="38">
+      <c r="AJ26" s="40">
         <f>SUM(AJ20:AJ25)</f>
         <v/>
       </c>
-      <c r="AK26" s="38">
+      <c r="AK26" s="40">
         <f>SUM(AK20:AK25)</f>
         <v/>
       </c>
-      <c r="AL26" s="38">
+      <c r="AL26" s="40">
         <f>SUM(AL20:AL25)</f>
         <v/>
       </c>
-      <c r="AM26" s="38">
+      <c r="AM26" s="40">
         <f>SUM(AM20:AM25)</f>
         <v/>
       </c>
-      <c r="AO26" s="38">
+      <c r="AO26" s="40">
         <f>SUM(D26:O26)</f>
         <v/>
       </c>
-      <c r="AP26" s="38">
+      <c r="AP26" s="40">
         <f>SUM(P26:AA26)</f>
         <v/>
       </c>
-      <c r="AQ26" s="38">
+      <c r="AQ26" s="40">
         <f>SUM(AB26:AM26)</f>
         <v/>
       </c>
@@ -11973,147 +12174,147 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="37">
         <f>IF(D6=1,Inputs!$B$20,C27*(1+Inputs!$B$21*Inputs!$B$22^(D6-1)))</f>
         <v/>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="37">
         <f>IF(E6=1,Inputs!$B$20,D27*(1+Inputs!$B$21*Inputs!$B$22^(E6-1)))</f>
         <v/>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="37">
         <f>IF(F6=1,Inputs!$B$20,E27*(1+Inputs!$B$21*Inputs!$B$22^(F6-1)))</f>
         <v/>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="37">
         <f>IF(G6=1,Inputs!$B$20,F27*(1+Inputs!$B$21*Inputs!$B$22^(G6-1)))</f>
         <v/>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="37">
         <f>IF(H6=1,Inputs!$B$20,G27*(1+Inputs!$B$21*Inputs!$B$22^(H6-1)))</f>
         <v/>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="37">
         <f>IF(I6=1,Inputs!$B$20,H27*(1+Inputs!$B$21*Inputs!$B$22^(I6-1)))</f>
         <v/>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="37">
         <f>IF(J6=1,Inputs!$B$20,I27*(1+Inputs!$B$21*Inputs!$B$22^(J6-1)))</f>
         <v/>
       </c>
-      <c r="K27" s="35">
+      <c r="K27" s="37">
         <f>IF(K6=1,Inputs!$B$20,J27*(1+Inputs!$B$21*Inputs!$B$22^(K6-1)))</f>
         <v/>
       </c>
-      <c r="L27" s="35">
+      <c r="L27" s="37">
         <f>IF(L6=1,Inputs!$B$20,K27*(1+Inputs!$B$21*Inputs!$B$22^(L6-1)))</f>
         <v/>
       </c>
-      <c r="M27" s="35">
+      <c r="M27" s="37">
         <f>IF(M6=1,Inputs!$B$20,L27*(1+Inputs!$B$21*Inputs!$B$22^(M6-1)))</f>
         <v/>
       </c>
-      <c r="N27" s="35">
+      <c r="N27" s="37">
         <f>IF(N6=1,Inputs!$B$20,M27*(1+Inputs!$B$21*Inputs!$B$22^(N6-1)))</f>
         <v/>
       </c>
-      <c r="O27" s="35">
+      <c r="O27" s="37">
         <f>IF(O6=1,Inputs!$B$20,N27*(1+Inputs!$B$21*Inputs!$B$22^(O6-1)))</f>
         <v/>
       </c>
-      <c r="P27" s="35">
+      <c r="P27" s="37">
         <f>IF(P6=1,Inputs!$B$20,O27*(1+Inputs!$B$21*Inputs!$B$22^(P6-1)))</f>
         <v/>
       </c>
-      <c r="Q27" s="35">
+      <c r="Q27" s="37">
         <f>IF(Q6=1,Inputs!$B$20,P27*(1+Inputs!$B$21*Inputs!$B$22^(Q6-1)))</f>
         <v/>
       </c>
-      <c r="R27" s="35">
+      <c r="R27" s="37">
         <f>IF(R6=1,Inputs!$B$20,Q27*(1+Inputs!$B$21*Inputs!$B$22^(R6-1)))</f>
         <v/>
       </c>
-      <c r="S27" s="35">
+      <c r="S27" s="37">
         <f>IF(S6=1,Inputs!$B$20,R27*(1+Inputs!$B$21*Inputs!$B$22^(S6-1)))</f>
         <v/>
       </c>
-      <c r="T27" s="35">
+      <c r="T27" s="37">
         <f>IF(T6=1,Inputs!$B$20,S27*(1+Inputs!$B$21*Inputs!$B$22^(T6-1)))</f>
         <v/>
       </c>
-      <c r="U27" s="35">
+      <c r="U27" s="37">
         <f>IF(U6=1,Inputs!$B$20,T27*(1+Inputs!$B$21*Inputs!$B$22^(U6-1)))</f>
         <v/>
       </c>
-      <c r="V27" s="35">
+      <c r="V27" s="37">
         <f>IF(V6=1,Inputs!$B$20,U27*(1+Inputs!$B$21*Inputs!$B$22^(V6-1)))</f>
         <v/>
       </c>
-      <c r="W27" s="35">
+      <c r="W27" s="37">
         <f>IF(W6=1,Inputs!$B$20,V27*(1+Inputs!$B$21*Inputs!$B$22^(W6-1)))</f>
         <v/>
       </c>
-      <c r="X27" s="35">
+      <c r="X27" s="37">
         <f>IF(X6=1,Inputs!$B$20,W27*(1+Inputs!$B$21*Inputs!$B$22^(X6-1)))</f>
         <v/>
       </c>
-      <c r="Y27" s="35">
+      <c r="Y27" s="37">
         <f>IF(Y6=1,Inputs!$B$20,X27*(1+Inputs!$B$21*Inputs!$B$22^(Y6-1)))</f>
         <v/>
       </c>
-      <c r="Z27" s="35">
+      <c r="Z27" s="37">
         <f>IF(Z6=1,Inputs!$B$20,Y27*(1+Inputs!$B$21*Inputs!$B$22^(Z6-1)))</f>
         <v/>
       </c>
-      <c r="AA27" s="35">
+      <c r="AA27" s="37">
         <f>IF(AA6=1,Inputs!$B$20,Z27*(1+Inputs!$B$21*Inputs!$B$22^(AA6-1)))</f>
         <v/>
       </c>
-      <c r="AB27" s="35">
+      <c r="AB27" s="37">
         <f>IF(AB6=1,Inputs!$B$20,AA27*(1+Inputs!$B$21*Inputs!$B$22^(AB6-1)))</f>
         <v/>
       </c>
-      <c r="AC27" s="35">
+      <c r="AC27" s="37">
         <f>IF(AC6=1,Inputs!$B$20,AB27*(1+Inputs!$B$21*Inputs!$B$22^(AC6-1)))</f>
         <v/>
       </c>
-      <c r="AD27" s="35">
+      <c r="AD27" s="37">
         <f>IF(AD6=1,Inputs!$B$20,AC27*(1+Inputs!$B$21*Inputs!$B$22^(AD6-1)))</f>
         <v/>
       </c>
-      <c r="AE27" s="35">
+      <c r="AE27" s="37">
         <f>IF(AE6=1,Inputs!$B$20,AD27*(1+Inputs!$B$21*Inputs!$B$22^(AE6-1)))</f>
         <v/>
       </c>
-      <c r="AF27" s="35">
+      <c r="AF27" s="37">
         <f>IF(AF6=1,Inputs!$B$20,AE27*(1+Inputs!$B$21*Inputs!$B$22^(AF6-1)))</f>
         <v/>
       </c>
-      <c r="AG27" s="35">
+      <c r="AG27" s="37">
         <f>IF(AG6=1,Inputs!$B$20,AF27*(1+Inputs!$B$21*Inputs!$B$22^(AG6-1)))</f>
         <v/>
       </c>
-      <c r="AH27" s="35">
+      <c r="AH27" s="37">
         <f>IF(AH6=1,Inputs!$B$20,AG27*(1+Inputs!$B$21*Inputs!$B$22^(AH6-1)))</f>
         <v/>
       </c>
-      <c r="AI27" s="35">
+      <c r="AI27" s="37">
         <f>IF(AI6=1,Inputs!$B$20,AH27*(1+Inputs!$B$21*Inputs!$B$22^(AI6-1)))</f>
         <v/>
       </c>
-      <c r="AJ27" s="35">
+      <c r="AJ27" s="37">
         <f>IF(AJ6=1,Inputs!$B$20,AI27*(1+Inputs!$B$21*Inputs!$B$22^(AJ6-1)))</f>
         <v/>
       </c>
-      <c r="AK27" s="35">
+      <c r="AK27" s="37">
         <f>IF(AK6=1,Inputs!$B$20,AJ27*(1+Inputs!$B$21*Inputs!$B$22^(AK6-1)))</f>
         <v/>
       </c>
-      <c r="AL27" s="35">
+      <c r="AL27" s="37">
         <f>IF(AL6=1,Inputs!$B$20,AK27*(1+Inputs!$B$21*Inputs!$B$22^(AL6-1)))</f>
         <v/>
       </c>
-      <c r="AM27" s="35">
+      <c r="AM27" s="37">
         <f>IF(AM6=1,Inputs!$B$20,AL27*(1+Inputs!$B$21*Inputs!$B$22^(AM6-1)))</f>
         <v/>
       </c>
@@ -12129,159 +12330,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="40">
         <f>D27*D9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="40">
         <f>E27*E9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="F28" s="38">
+      <c r="F28" s="40">
         <f>F27*F9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="G28" s="38">
+      <c r="G28" s="40">
         <f>G27*G9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="H28" s="38">
+      <c r="H28" s="40">
         <f>H27*H9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="I28" s="38">
+      <c r="I28" s="40">
         <f>I27*I9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="J28" s="38">
+      <c r="J28" s="40">
         <f>J27*J9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="40">
         <f>K27*K9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="L28" s="38">
+      <c r="L28" s="40">
         <f>L27*L9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="M28" s="38">
+      <c r="M28" s="40">
         <f>M27*M9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="N28" s="38">
+      <c r="N28" s="40">
         <f>N27*N9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="O28" s="38">
+      <c r="O28" s="40">
         <f>O27*O9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="P28" s="38">
+      <c r="P28" s="40">
         <f>P27*P9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="Q28" s="38">
+      <c r="Q28" s="40">
         <f>Q27*Q9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="R28" s="38">
+      <c r="R28" s="40">
         <f>R27*R9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="S28" s="38">
+      <c r="S28" s="40">
         <f>S27*S9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="T28" s="38">
+      <c r="T28" s="40">
         <f>T27*T9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="U28" s="38">
+      <c r="U28" s="40">
         <f>U27*U9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="V28" s="38">
+      <c r="V28" s="40">
         <f>V27*V9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="W28" s="38">
+      <c r="W28" s="40">
         <f>W27*W9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="X28" s="38">
+      <c r="X28" s="40">
         <f>X27*X9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="Y28" s="38">
+      <c r="Y28" s="40">
         <f>Y27*Y9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="Z28" s="38">
+      <c r="Z28" s="40">
         <f>Z27*Z9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AA28" s="38">
+      <c r="AA28" s="40">
         <f>AA27*AA9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AB28" s="38">
+      <c r="AB28" s="40">
         <f>AB27*AB9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AC28" s="38">
+      <c r="AC28" s="40">
         <f>AC27*AC9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AD28" s="38">
+      <c r="AD28" s="40">
         <f>AD27*AD9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AE28" s="38">
+      <c r="AE28" s="40">
         <f>AE27*AE9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AF28" s="38">
+      <c r="AF28" s="40">
         <f>AF27*AF9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AG28" s="38">
+      <c r="AG28" s="40">
         <f>AG27*AG9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AH28" s="38">
+      <c r="AH28" s="40">
         <f>AH27*AH9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AI28" s="38">
+      <c r="AI28" s="40">
         <f>AI27*AI9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AJ28" s="38">
+      <c r="AJ28" s="40">
         <f>AJ27*AJ9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AK28" s="38">
+      <c r="AK28" s="40">
         <f>AK27*AK9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AL28" s="38">
+      <c r="AL28" s="40">
         <f>AL27*AL9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AM28" s="38">
+      <c r="AM28" s="40">
         <f>AM27*AM9*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AO28" s="38">
+      <c r="AO28" s="40">
         <f>SUM(D28:O28)</f>
         <v/>
       </c>
-      <c r="AP28" s="38">
+      <c r="AP28" s="40">
         <f>SUM(P28:AA28)</f>
         <v/>
       </c>
-      <c r="AQ28" s="38">
+      <c r="AQ28" s="40">
         <f>SUM(AB28:AM28)</f>
         <v/>
       </c>
@@ -12297,159 +12498,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D29" s="35">
+      <c r="D29" s="37">
         <f>C44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="E29" s="35">
+      <c r="E29" s="37">
         <f>D44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="F29" s="35">
+      <c r="F29" s="37">
         <f>E44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="37">
         <f>F44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="H29" s="35">
+      <c r="H29" s="37">
         <f>G44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="I29" s="35">
+      <c r="I29" s="37">
         <f>H44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="37">
         <f>I44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="37">
         <f>J44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="L29" s="35">
+      <c r="L29" s="37">
         <f>K44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="M29" s="35">
+      <c r="M29" s="37">
         <f>L44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="N29" s="35">
+      <c r="N29" s="37">
         <f>M44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="O29" s="35">
+      <c r="O29" s="37">
         <f>N44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="P29" s="35">
+      <c r="P29" s="37">
         <f>O44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="Q29" s="35">
+      <c r="Q29" s="37">
         <f>P44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="R29" s="35">
+      <c r="R29" s="37">
         <f>Q44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="S29" s="35">
+      <c r="S29" s="37">
         <f>R44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="T29" s="35">
+      <c r="T29" s="37">
         <f>S44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="U29" s="35">
+      <c r="U29" s="37">
         <f>T44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="V29" s="35">
+      <c r="V29" s="37">
         <f>U44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="W29" s="35">
+      <c r="W29" s="37">
         <f>V44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="X29" s="35">
+      <c r="X29" s="37">
         <f>W44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="Y29" s="35">
+      <c r="Y29" s="37">
         <f>X44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="Z29" s="35">
+      <c r="Z29" s="37">
         <f>Y44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AA29" s="35">
+      <c r="AA29" s="37">
         <f>Z44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AB29" s="35">
+      <c r="AB29" s="37">
         <f>AA44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AC29" s="35">
+      <c r="AC29" s="37">
         <f>AB44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AD29" s="35">
+      <c r="AD29" s="37">
         <f>AC44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AE29" s="35">
+      <c r="AE29" s="37">
         <f>AD44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AF29" s="35">
+      <c r="AF29" s="37">
         <f>AE44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AG29" s="35">
+      <c r="AG29" s="37">
         <f>AF44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AH29" s="35">
+      <c r="AH29" s="37">
         <f>AG44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AI29" s="35">
+      <c r="AI29" s="37">
         <f>AH44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AJ29" s="35">
+      <c r="AJ29" s="37">
         <f>AI44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AK29" s="35">
+      <c r="AK29" s="37">
         <f>AJ44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AL29" s="35">
+      <c r="AL29" s="37">
         <f>AK44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AM29" s="35">
+      <c r="AM29" s="37">
         <f>AL44*Inputs!$B$23*Scenarios!$B$7</f>
         <v/>
       </c>
-      <c r="AO29" s="35">
+      <c r="AO29" s="37">
         <f>SUM(D29:O29)</f>
         <v/>
       </c>
-      <c r="AP29" s="35">
+      <c r="AP29" s="37">
         <f>SUM(P29:AA29)</f>
         <v/>
       </c>
-      <c r="AQ29" s="35">
+      <c r="AQ29" s="37">
         <f>SUM(AB29:AM29)</f>
         <v/>
       </c>
@@ -12465,159 +12666,159 @@
           <t>visits</t>
         </is>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="40">
         <f>D26+D28+D29</f>
         <v/>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="40">
         <f>E26+E28+E29</f>
         <v/>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="40">
         <f>F26+F28+F29</f>
         <v/>
       </c>
-      <c r="G30" s="38">
+      <c r="G30" s="40">
         <f>G26+G28+G29</f>
         <v/>
       </c>
-      <c r="H30" s="38">
+      <c r="H30" s="40">
         <f>H26+H28+H29</f>
         <v/>
       </c>
-      <c r="I30" s="38">
+      <c r="I30" s="40">
         <f>I26+I28+I29</f>
         <v/>
       </c>
-      <c r="J30" s="38">
+      <c r="J30" s="40">
         <f>J26+J28+J29</f>
         <v/>
       </c>
-      <c r="K30" s="38">
+      <c r="K30" s="40">
         <f>K26+K28+K29</f>
         <v/>
       </c>
-      <c r="L30" s="38">
+      <c r="L30" s="40">
         <f>L26+L28+L29</f>
         <v/>
       </c>
-      <c r="M30" s="38">
+      <c r="M30" s="40">
         <f>M26+M28+M29</f>
         <v/>
       </c>
-      <c r="N30" s="38">
+      <c r="N30" s="40">
         <f>N26+N28+N29</f>
         <v/>
       </c>
-      <c r="O30" s="38">
+      <c r="O30" s="40">
         <f>O26+O28+O29</f>
         <v/>
       </c>
-      <c r="P30" s="38">
+      <c r="P30" s="40">
         <f>P26+P28+P29</f>
         <v/>
       </c>
-      <c r="Q30" s="38">
+      <c r="Q30" s="40">
         <f>Q26+Q28+Q29</f>
         <v/>
       </c>
-      <c r="R30" s="38">
+      <c r="R30" s="40">
         <f>R26+R28+R29</f>
         <v/>
       </c>
-      <c r="S30" s="38">
+      <c r="S30" s="40">
         <f>S26+S28+S29</f>
         <v/>
       </c>
-      <c r="T30" s="38">
+      <c r="T30" s="40">
         <f>T26+T28+T29</f>
         <v/>
       </c>
-      <c r="U30" s="38">
+      <c r="U30" s="40">
         <f>U26+U28+U29</f>
         <v/>
       </c>
-      <c r="V30" s="38">
+      <c r="V30" s="40">
         <f>V26+V28+V29</f>
         <v/>
       </c>
-      <c r="W30" s="38">
+      <c r="W30" s="40">
         <f>W26+W28+W29</f>
         <v/>
       </c>
-      <c r="X30" s="38">
+      <c r="X30" s="40">
         <f>X26+X28+X29</f>
         <v/>
       </c>
-      <c r="Y30" s="38">
+      <c r="Y30" s="40">
         <f>Y26+Y28+Y29</f>
         <v/>
       </c>
-      <c r="Z30" s="38">
+      <c r="Z30" s="40">
         <f>Z26+Z28+Z29</f>
         <v/>
       </c>
-      <c r="AA30" s="38">
+      <c r="AA30" s="40">
         <f>AA26+AA28+AA29</f>
         <v/>
       </c>
-      <c r="AB30" s="38">
+      <c r="AB30" s="40">
         <f>AB26+AB28+AB29</f>
         <v/>
       </c>
-      <c r="AC30" s="38">
+      <c r="AC30" s="40">
         <f>AC26+AC28+AC29</f>
         <v/>
       </c>
-      <c r="AD30" s="38">
+      <c r="AD30" s="40">
         <f>AD26+AD28+AD29</f>
         <v/>
       </c>
-      <c r="AE30" s="38">
+      <c r="AE30" s="40">
         <f>AE26+AE28+AE29</f>
         <v/>
       </c>
-      <c r="AF30" s="38">
+      <c r="AF30" s="40">
         <f>AF26+AF28+AF29</f>
         <v/>
       </c>
-      <c r="AG30" s="38">
+      <c r="AG30" s="40">
         <f>AG26+AG28+AG29</f>
         <v/>
       </c>
-      <c r="AH30" s="38">
+      <c r="AH30" s="40">
         <f>AH26+AH28+AH29</f>
         <v/>
       </c>
-      <c r="AI30" s="38">
+      <c r="AI30" s="40">
         <f>AI26+AI28+AI29</f>
         <v/>
       </c>
-      <c r="AJ30" s="38">
+      <c r="AJ30" s="40">
         <f>AJ26+AJ28+AJ29</f>
         <v/>
       </c>
-      <c r="AK30" s="38">
+      <c r="AK30" s="40">
         <f>AK26+AK28+AK29</f>
         <v/>
       </c>
-      <c r="AL30" s="38">
+      <c r="AL30" s="40">
         <f>AL26+AL28+AL29</f>
         <v/>
       </c>
-      <c r="AM30" s="38">
+      <c r="AM30" s="40">
         <f>AM26+AM28+AM29</f>
         <v/>
       </c>
-      <c r="AO30" s="38">
+      <c r="AO30" s="40">
         <f>SUM(D30:O30)</f>
         <v/>
       </c>
-      <c r="AP30" s="38">
+      <c r="AP30" s="40">
         <f>SUM(P30:AA30)</f>
         <v/>
       </c>
-      <c r="AQ30" s="38">
+      <c r="AQ30" s="40">
         <f>SUM(AB30:AM30)</f>
         <v/>
       </c>
@@ -12682,159 +12883,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="37">
         <f>D30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="E32" s="35">
+      <c r="E32" s="37">
         <f>E30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="37">
         <f>F30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="37">
         <f>G30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="H32" s="35">
+      <c r="H32" s="37">
         <f>H30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="I32" s="35">
+      <c r="I32" s="37">
         <f>I30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="37">
         <f>J30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="K32" s="35">
+      <c r="K32" s="37">
         <f>K30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="L32" s="35">
+      <c r="L32" s="37">
         <f>L30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="M32" s="35">
+      <c r="M32" s="37">
         <f>M30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="N32" s="35">
+      <c r="N32" s="37">
         <f>N30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="O32" s="35">
+      <c r="O32" s="37">
         <f>O30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="P32" s="35">
+      <c r="P32" s="37">
         <f>P30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="Q32" s="35">
+      <c r="Q32" s="37">
         <f>Q30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="R32" s="35">
+      <c r="R32" s="37">
         <f>R30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="S32" s="35">
+      <c r="S32" s="37">
         <f>S30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="T32" s="35">
+      <c r="T32" s="37">
         <f>T30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="U32" s="35">
+      <c r="U32" s="37">
         <f>U30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="V32" s="35">
+      <c r="V32" s="37">
         <f>V30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="W32" s="35">
+      <c r="W32" s="37">
         <f>W30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="X32" s="35">
+      <c r="X32" s="37">
         <f>X30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="Y32" s="35">
+      <c r="Y32" s="37">
         <f>Y30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="Z32" s="35">
+      <c r="Z32" s="37">
         <f>Z30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AA32" s="35">
+      <c r="AA32" s="37">
         <f>AA30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AB32" s="35">
+      <c r="AB32" s="37">
         <f>AB30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AC32" s="35">
+      <c r="AC32" s="37">
         <f>AC30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AD32" s="35">
+      <c r="AD32" s="37">
         <f>AD30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AE32" s="35">
+      <c r="AE32" s="37">
         <f>AE30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AF32" s="35">
+      <c r="AF32" s="37">
         <f>AF30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AG32" s="35">
+      <c r="AG32" s="37">
         <f>AG30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AH32" s="35">
+      <c r="AH32" s="37">
         <f>AH30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AI32" s="35">
+      <c r="AI32" s="37">
         <f>AI30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AJ32" s="35">
+      <c r="AJ32" s="37">
         <f>AJ30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AK32" s="35">
+      <c r="AK32" s="37">
         <f>AK30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AL32" s="35">
+      <c r="AL32" s="37">
         <f>AL30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AM32" s="35">
+      <c r="AM32" s="37">
         <f>AM30*Inputs!$B$15</f>
         <v/>
       </c>
-      <c r="AO32" s="35">
+      <c r="AO32" s="37">
         <f>SUM(D32:O32)</f>
         <v/>
       </c>
-      <c r="AP32" s="35">
+      <c r="AP32" s="37">
         <f>SUM(P32:AA32)</f>
         <v/>
       </c>
-      <c r="AQ32" s="35">
+      <c r="AQ32" s="37">
         <f>SUM(AB32:AM32)</f>
         <v/>
       </c>
@@ -12850,159 +13051,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="37">
         <f>SUMPRODUCT(D20:D25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="37">
         <f>SUMPRODUCT(E20:E25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="37">
         <f>SUMPRODUCT(F20:F25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="37">
         <f>SUMPRODUCT(G20:G25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="37">
         <f>SUMPRODUCT(H20:H25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="37">
         <f>SUMPRODUCT(I20:I25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="37">
         <f>SUMPRODUCT(J20:J25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="37">
         <f>SUMPRODUCT(K20:K25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="37">
         <f>SUMPRODUCT(L20:L25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="37">
         <f>SUMPRODUCT(M20:M25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="37">
         <f>SUMPRODUCT(N20:N25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="37">
         <f>SUMPRODUCT(O20:O25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="37">
         <f>SUMPRODUCT(P20:P25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="37">
         <f>SUMPRODUCT(Q20:Q25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="37">
         <f>SUMPRODUCT(R20:R25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="37">
         <f>SUMPRODUCT(S20:S25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="37">
         <f>SUMPRODUCT(T20:T25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="U33" s="35">
+      <c r="U33" s="37">
         <f>SUMPRODUCT(U20:U25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="V33" s="35">
+      <c r="V33" s="37">
         <f>SUMPRODUCT(V20:V25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="W33" s="35">
+      <c r="W33" s="37">
         <f>SUMPRODUCT(W20:W25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="X33" s="35">
+      <c r="X33" s="37">
         <f>SUMPRODUCT(X20:X25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="Y33" s="35">
+      <c r="Y33" s="37">
         <f>SUMPRODUCT(Y20:Y25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="Z33" s="35">
+      <c r="Z33" s="37">
         <f>SUMPRODUCT(Z20:Z25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AA33" s="35">
+      <c r="AA33" s="37">
         <f>SUMPRODUCT(AA20:AA25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AB33" s="35">
+      <c r="AB33" s="37">
         <f>SUMPRODUCT(AB20:AB25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AC33" s="35">
+      <c r="AC33" s="37">
         <f>SUMPRODUCT(AC20:AC25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AD33" s="35">
+      <c r="AD33" s="37">
         <f>SUMPRODUCT(AD20:AD25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AE33" s="35">
+      <c r="AE33" s="37">
         <f>SUMPRODUCT(AE20:AE25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AF33" s="35">
+      <c r="AF33" s="37">
         <f>SUMPRODUCT(AF20:AF25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AG33" s="35">
+      <c r="AG33" s="37">
         <f>SUMPRODUCT(AG20:AG25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AH33" s="35">
+      <c r="AH33" s="37">
         <f>SUMPRODUCT(AH20:AH25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AI33" s="35">
+      <c r="AI33" s="37">
         <f>SUMPRODUCT(AI20:AI25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AJ33" s="35">
+      <c r="AJ33" s="37">
         <f>SUMPRODUCT(AJ20:AJ25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AK33" s="35">
+      <c r="AK33" s="37">
         <f>SUMPRODUCT(AK20:AK25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AL33" s="35">
+      <c r="AL33" s="37">
         <f>SUMPRODUCT(AL20:AL25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AM33" s="35">
+      <c r="AM33" s="37">
         <f>SUMPRODUCT(AM20:AM25,'Unit Economics'!$E$15:$E$20)</f>
         <v/>
       </c>
-      <c r="AO33" s="35">
+      <c r="AO33" s="37">
         <f>SUM(D33:O33)</f>
         <v/>
       </c>
-      <c r="AP33" s="35">
+      <c r="AP33" s="37">
         <f>SUM(P33:AA33)</f>
         <v/>
       </c>
-      <c r="AQ33" s="35">
+      <c r="AQ33" s="37">
         <f>SUM(AB33:AM33)</f>
         <v/>
       </c>
@@ -13018,159 +13219,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="37">
         <f>Inputs!$B$12*(D28+D29)</f>
         <v/>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="37">
         <f>Inputs!$B$12*(E28+E29)</f>
         <v/>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="37">
         <f>Inputs!$B$12*(F28+F29)</f>
         <v/>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="37">
         <f>Inputs!$B$12*(G28+G29)</f>
         <v/>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="37">
         <f>Inputs!$B$12*(H28+H29)</f>
         <v/>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="37">
         <f>Inputs!$B$12*(I28+I29)</f>
         <v/>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="37">
         <f>Inputs!$B$12*(J28+J29)</f>
         <v/>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="37">
         <f>Inputs!$B$12*(K28+K29)</f>
         <v/>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="37">
         <f>Inputs!$B$12*(L28+L29)</f>
         <v/>
       </c>
-      <c r="M34" s="35">
+      <c r="M34" s="37">
         <f>Inputs!$B$12*(M28+M29)</f>
         <v/>
       </c>
-      <c r="N34" s="35">
+      <c r="N34" s="37">
         <f>Inputs!$B$12*(N28+N29)</f>
         <v/>
       </c>
-      <c r="O34" s="35">
+      <c r="O34" s="37">
         <f>Inputs!$B$12*(O28+O29)</f>
         <v/>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="37">
         <f>Inputs!$B$12*(P28+P29)</f>
         <v/>
       </c>
-      <c r="Q34" s="35">
+      <c r="Q34" s="37">
         <f>Inputs!$B$12*(Q28+Q29)</f>
         <v/>
       </c>
-      <c r="R34" s="35">
+      <c r="R34" s="37">
         <f>Inputs!$B$12*(R28+R29)</f>
         <v/>
       </c>
-      <c r="S34" s="35">
+      <c r="S34" s="37">
         <f>Inputs!$B$12*(S28+S29)</f>
         <v/>
       </c>
-      <c r="T34" s="35">
+      <c r="T34" s="37">
         <f>Inputs!$B$12*(T28+T29)</f>
         <v/>
       </c>
-      <c r="U34" s="35">
+      <c r="U34" s="37">
         <f>Inputs!$B$12*(U28+U29)</f>
         <v/>
       </c>
-      <c r="V34" s="35">
+      <c r="V34" s="37">
         <f>Inputs!$B$12*(V28+V29)</f>
         <v/>
       </c>
-      <c r="W34" s="35">
+      <c r="W34" s="37">
         <f>Inputs!$B$12*(W28+W29)</f>
         <v/>
       </c>
-      <c r="X34" s="35">
+      <c r="X34" s="37">
         <f>Inputs!$B$12*(X28+X29)</f>
         <v/>
       </c>
-      <c r="Y34" s="35">
+      <c r="Y34" s="37">
         <f>Inputs!$B$12*(Y28+Y29)</f>
         <v/>
       </c>
-      <c r="Z34" s="35">
+      <c r="Z34" s="37">
         <f>Inputs!$B$12*(Z28+Z29)</f>
         <v/>
       </c>
-      <c r="AA34" s="35">
+      <c r="AA34" s="37">
         <f>Inputs!$B$12*(AA28+AA29)</f>
         <v/>
       </c>
-      <c r="AB34" s="35">
+      <c r="AB34" s="37">
         <f>Inputs!$B$12*(AB28+AB29)</f>
         <v/>
       </c>
-      <c r="AC34" s="35">
+      <c r="AC34" s="37">
         <f>Inputs!$B$12*(AC28+AC29)</f>
         <v/>
       </c>
-      <c r="AD34" s="35">
+      <c r="AD34" s="37">
         <f>Inputs!$B$12*(AD28+AD29)</f>
         <v/>
       </c>
-      <c r="AE34" s="35">
+      <c r="AE34" s="37">
         <f>Inputs!$B$12*(AE28+AE29)</f>
         <v/>
       </c>
-      <c r="AF34" s="35">
+      <c r="AF34" s="37">
         <f>Inputs!$B$12*(AF28+AF29)</f>
         <v/>
       </c>
-      <c r="AG34" s="35">
+      <c r="AG34" s="37">
         <f>Inputs!$B$12*(AG28+AG29)</f>
         <v/>
       </c>
-      <c r="AH34" s="35">
+      <c r="AH34" s="37">
         <f>Inputs!$B$12*(AH28+AH29)</f>
         <v/>
       </c>
-      <c r="AI34" s="35">
+      <c r="AI34" s="37">
         <f>Inputs!$B$12*(AI28+AI29)</f>
         <v/>
       </c>
-      <c r="AJ34" s="35">
+      <c r="AJ34" s="37">
         <f>Inputs!$B$12*(AJ28+AJ29)</f>
         <v/>
       </c>
-      <c r="AK34" s="35">
+      <c r="AK34" s="37">
         <f>Inputs!$B$12*(AK28+AK29)</f>
         <v/>
       </c>
-      <c r="AL34" s="35">
+      <c r="AL34" s="37">
         <f>Inputs!$B$12*(AL28+AL29)</f>
         <v/>
       </c>
-      <c r="AM34" s="35">
+      <c r="AM34" s="37">
         <f>Inputs!$B$12*(AM28+AM29)</f>
         <v/>
       </c>
-      <c r="AO34" s="35">
+      <c r="AO34" s="37">
         <f>SUM(D34:O34)</f>
         <v/>
       </c>
-      <c r="AP34" s="35">
+      <c r="AP34" s="37">
         <f>SUM(P34:AA34)</f>
         <v/>
       </c>
-      <c r="AQ34" s="35">
+      <c r="AQ34" s="37">
         <f>SUM(AB34:AM34)</f>
         <v/>
       </c>
@@ -13186,159 +13387,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D35" s="38">
+      <c r="D35" s="40">
         <f>D33+D34</f>
         <v/>
       </c>
-      <c r="E35" s="38">
+      <c r="E35" s="40">
         <f>E33+E34</f>
         <v/>
       </c>
-      <c r="F35" s="38">
+      <c r="F35" s="40">
         <f>F33+F34</f>
         <v/>
       </c>
-      <c r="G35" s="38">
+      <c r="G35" s="40">
         <f>G33+G34</f>
         <v/>
       </c>
-      <c r="H35" s="38">
+      <c r="H35" s="40">
         <f>H33+H34</f>
         <v/>
       </c>
-      <c r="I35" s="38">
+      <c r="I35" s="40">
         <f>I33+I34</f>
         <v/>
       </c>
-      <c r="J35" s="38">
+      <c r="J35" s="40">
         <f>J33+J34</f>
         <v/>
       </c>
-      <c r="K35" s="38">
+      <c r="K35" s="40">
         <f>K33+K34</f>
         <v/>
       </c>
-      <c r="L35" s="38">
+      <c r="L35" s="40">
         <f>L33+L34</f>
         <v/>
       </c>
-      <c r="M35" s="38">
+      <c r="M35" s="40">
         <f>M33+M34</f>
         <v/>
       </c>
-      <c r="N35" s="38">
+      <c r="N35" s="40">
         <f>N33+N34</f>
         <v/>
       </c>
-      <c r="O35" s="38">
+      <c r="O35" s="40">
         <f>O33+O34</f>
         <v/>
       </c>
-      <c r="P35" s="38">
+      <c r="P35" s="40">
         <f>P33+P34</f>
         <v/>
       </c>
-      <c r="Q35" s="38">
+      <c r="Q35" s="40">
         <f>Q33+Q34</f>
         <v/>
       </c>
-      <c r="R35" s="38">
+      <c r="R35" s="40">
         <f>R33+R34</f>
         <v/>
       </c>
-      <c r="S35" s="38">
+      <c r="S35" s="40">
         <f>S33+S34</f>
         <v/>
       </c>
-      <c r="T35" s="38">
+      <c r="T35" s="40">
         <f>T33+T34</f>
         <v/>
       </c>
-      <c r="U35" s="38">
+      <c r="U35" s="40">
         <f>U33+U34</f>
         <v/>
       </c>
-      <c r="V35" s="38">
+      <c r="V35" s="40">
         <f>V33+V34</f>
         <v/>
       </c>
-      <c r="W35" s="38">
+      <c r="W35" s="40">
         <f>W33+W34</f>
         <v/>
       </c>
-      <c r="X35" s="38">
+      <c r="X35" s="40">
         <f>X33+X34</f>
         <v/>
       </c>
-      <c r="Y35" s="38">
+      <c r="Y35" s="40">
         <f>Y33+Y34</f>
         <v/>
       </c>
-      <c r="Z35" s="38">
+      <c r="Z35" s="40">
         <f>Z33+Z34</f>
         <v/>
       </c>
-      <c r="AA35" s="38">
+      <c r="AA35" s="40">
         <f>AA33+AA34</f>
         <v/>
       </c>
-      <c r="AB35" s="38">
+      <c r="AB35" s="40">
         <f>AB33+AB34</f>
         <v/>
       </c>
-      <c r="AC35" s="38">
+      <c r="AC35" s="40">
         <f>AC33+AC34</f>
         <v/>
       </c>
-      <c r="AD35" s="38">
+      <c r="AD35" s="40">
         <f>AD33+AD34</f>
         <v/>
       </c>
-      <c r="AE35" s="38">
+      <c r="AE35" s="40">
         <f>AE33+AE34</f>
         <v/>
       </c>
-      <c r="AF35" s="38">
+      <c r="AF35" s="40">
         <f>AF33+AF34</f>
         <v/>
       </c>
-      <c r="AG35" s="38">
+      <c r="AG35" s="40">
         <f>AG33+AG34</f>
         <v/>
       </c>
-      <c r="AH35" s="38">
+      <c r="AH35" s="40">
         <f>AH33+AH34</f>
         <v/>
       </c>
-      <c r="AI35" s="38">
+      <c r="AI35" s="40">
         <f>AI33+AI34</f>
         <v/>
       </c>
-      <c r="AJ35" s="38">
+      <c r="AJ35" s="40">
         <f>AJ33+AJ34</f>
         <v/>
       </c>
-      <c r="AK35" s="38">
+      <c r="AK35" s="40">
         <f>AK33+AK34</f>
         <v/>
       </c>
-      <c r="AL35" s="38">
+      <c r="AL35" s="40">
         <f>AL33+AL34</f>
         <v/>
       </c>
-      <c r="AM35" s="38">
+      <c r="AM35" s="40">
         <f>AM33+AM34</f>
         <v/>
       </c>
-      <c r="AO35" s="38">
+      <c r="AO35" s="40">
         <f>SUM(D35:O35)</f>
         <v/>
       </c>
-      <c r="AP35" s="38">
+      <c r="AP35" s="40">
         <f>SUM(P35:AA35)</f>
         <v/>
       </c>
-      <c r="AQ35" s="38">
+      <c r="AQ35" s="40">
         <f>SUM(AB35:AM35)</f>
         <v/>
       </c>
@@ -13354,159 +13555,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="37">
         <f>D35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="37">
         <f>E35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="37">
         <f>F35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="37">
         <f>G35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="37">
         <f>H35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="37">
         <f>I35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="37">
         <f>J35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="37">
         <f>K35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="37">
         <f>L35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="37">
         <f>M35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="37">
         <f>N35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="37">
         <f>O35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="37">
         <f>P35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="37">
         <f>Q35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="R36" s="35">
+      <c r="R36" s="37">
         <f>R35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="S36" s="35">
+      <c r="S36" s="37">
         <f>S35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="T36" s="35">
+      <c r="T36" s="37">
         <f>T35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="U36" s="35">
+      <c r="U36" s="37">
         <f>U35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="37">
         <f>V35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="W36" s="35">
+      <c r="W36" s="37">
         <f>W35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="X36" s="35">
+      <c r="X36" s="37">
         <f>X35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="Y36" s="35">
+      <c r="Y36" s="37">
         <f>Y35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="Z36" s="35">
+      <c r="Z36" s="37">
         <f>Z35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AA36" s="35">
+      <c r="AA36" s="37">
         <f>AA35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AB36" s="35">
+      <c r="AB36" s="37">
         <f>AB35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AC36" s="35">
+      <c r="AC36" s="37">
         <f>AC35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AD36" s="35">
+      <c r="AD36" s="37">
         <f>AD35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AE36" s="35">
+      <c r="AE36" s="37">
         <f>AE35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AF36" s="35">
+      <c r="AF36" s="37">
         <f>AF35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AG36" s="35">
+      <c r="AG36" s="37">
         <f>AG35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AH36" s="35">
+      <c r="AH36" s="37">
         <f>AH35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AI36" s="35">
+      <c r="AI36" s="37">
         <f>AI35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AJ36" s="35">
+      <c r="AJ36" s="37">
         <f>AJ35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AK36" s="35">
+      <c r="AK36" s="37">
         <f>AK35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AL36" s="35">
+      <c r="AL36" s="37">
         <f>AL35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AM36" s="35">
+      <c r="AM36" s="37">
         <f>AM35*Inputs!$B$13</f>
         <v/>
       </c>
-      <c r="AO36" s="35">
+      <c r="AO36" s="37">
         <f>SUM(D36:O36)</f>
         <v/>
       </c>
-      <c r="AP36" s="35">
+      <c r="AP36" s="37">
         <f>SUM(P36:AA36)</f>
         <v/>
       </c>
-      <c r="AQ36" s="35">
+      <c r="AQ36" s="37">
         <f>SUM(AB36:AM36)</f>
         <v/>
       </c>
@@ -13690,159 +13891,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="37">
         <f>SUMPRODUCT(D20:D25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*D37</f>
         <v/>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="37">
         <f>SUMPRODUCT(E20:E25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*E37</f>
         <v/>
       </c>
-      <c r="F38" s="35">
+      <c r="F38" s="37">
         <f>SUMPRODUCT(F20:F25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*F37</f>
         <v/>
       </c>
-      <c r="G38" s="35">
+      <c r="G38" s="37">
         <f>SUMPRODUCT(G20:G25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*G37</f>
         <v/>
       </c>
-      <c r="H38" s="35">
+      <c r="H38" s="37">
         <f>SUMPRODUCT(H20:H25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*H37</f>
         <v/>
       </c>
-      <c r="I38" s="35">
+      <c r="I38" s="37">
         <f>SUMPRODUCT(I20:I25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*I37</f>
         <v/>
       </c>
-      <c r="J38" s="35">
+      <c r="J38" s="37">
         <f>SUMPRODUCT(J20:J25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*J37</f>
         <v/>
       </c>
-      <c r="K38" s="35">
+      <c r="K38" s="37">
         <f>SUMPRODUCT(K20:K25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*K37</f>
         <v/>
       </c>
-      <c r="L38" s="35">
+      <c r="L38" s="37">
         <f>SUMPRODUCT(L20:L25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*L37</f>
         <v/>
       </c>
-      <c r="M38" s="35">
+      <c r="M38" s="37">
         <f>SUMPRODUCT(M20:M25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*M37</f>
         <v/>
       </c>
-      <c r="N38" s="35">
+      <c r="N38" s="37">
         <f>SUMPRODUCT(N20:N25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*N37</f>
         <v/>
       </c>
-      <c r="O38" s="35">
+      <c r="O38" s="37">
         <f>SUMPRODUCT(O20:O25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*O37</f>
         <v/>
       </c>
-      <c r="P38" s="35">
+      <c r="P38" s="37">
         <f>SUMPRODUCT(P20:P25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*P37</f>
         <v/>
       </c>
-      <c r="Q38" s="35">
+      <c r="Q38" s="37">
         <f>SUMPRODUCT(Q20:Q25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*Q37</f>
         <v/>
       </c>
-      <c r="R38" s="35">
+      <c r="R38" s="37">
         <f>SUMPRODUCT(R20:R25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*R37</f>
         <v/>
       </c>
-      <c r="S38" s="35">
+      <c r="S38" s="37">
         <f>SUMPRODUCT(S20:S25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*S37</f>
         <v/>
       </c>
-      <c r="T38" s="35">
+      <c r="T38" s="37">
         <f>SUMPRODUCT(T20:T25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*T37</f>
         <v/>
       </c>
-      <c r="U38" s="35">
+      <c r="U38" s="37">
         <f>SUMPRODUCT(U20:U25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*U37</f>
         <v/>
       </c>
-      <c r="V38" s="35">
+      <c r="V38" s="37">
         <f>SUMPRODUCT(V20:V25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*V37</f>
         <v/>
       </c>
-      <c r="W38" s="35">
+      <c r="W38" s="37">
         <f>SUMPRODUCT(W20:W25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*W37</f>
         <v/>
       </c>
-      <c r="X38" s="35">
+      <c r="X38" s="37">
         <f>SUMPRODUCT(X20:X25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*X37</f>
         <v/>
       </c>
-      <c r="Y38" s="35">
+      <c r="Y38" s="37">
         <f>SUMPRODUCT(Y20:Y25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*Y37</f>
         <v/>
       </c>
-      <c r="Z38" s="35">
+      <c r="Z38" s="37">
         <f>SUMPRODUCT(Z20:Z25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*Z37</f>
         <v/>
       </c>
-      <c r="AA38" s="35">
+      <c r="AA38" s="37">
         <f>SUMPRODUCT(AA20:AA25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AA37</f>
         <v/>
       </c>
-      <c r="AB38" s="35">
+      <c r="AB38" s="37">
         <f>SUMPRODUCT(AB20:AB25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AB37</f>
         <v/>
       </c>
-      <c r="AC38" s="35">
+      <c r="AC38" s="37">
         <f>SUMPRODUCT(AC20:AC25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AC37</f>
         <v/>
       </c>
-      <c r="AD38" s="35">
+      <c r="AD38" s="37">
         <f>SUMPRODUCT(AD20:AD25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AD37</f>
         <v/>
       </c>
-      <c r="AE38" s="35">
+      <c r="AE38" s="37">
         <f>SUMPRODUCT(AE20:AE25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AE37</f>
         <v/>
       </c>
-      <c r="AF38" s="35">
+      <c r="AF38" s="37">
         <f>SUMPRODUCT(AF20:AF25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AF37</f>
         <v/>
       </c>
-      <c r="AG38" s="35">
+      <c r="AG38" s="37">
         <f>SUMPRODUCT(AG20:AG25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AG37</f>
         <v/>
       </c>
-      <c r="AH38" s="35">
+      <c r="AH38" s="37">
         <f>SUMPRODUCT(AH20:AH25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AH37</f>
         <v/>
       </c>
-      <c r="AI38" s="35">
+      <c r="AI38" s="37">
         <f>SUMPRODUCT(AI20:AI25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AI37</f>
         <v/>
       </c>
-      <c r="AJ38" s="35">
+      <c r="AJ38" s="37">
         <f>SUMPRODUCT(AJ20:AJ25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AJ37</f>
         <v/>
       </c>
-      <c r="AK38" s="35">
+      <c r="AK38" s="37">
         <f>SUMPRODUCT(AK20:AK25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AK37</f>
         <v/>
       </c>
-      <c r="AL38" s="35">
+      <c r="AL38" s="37">
         <f>SUMPRODUCT(AL20:AL25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AL37</f>
         <v/>
       </c>
-      <c r="AM38" s="35">
+      <c r="AM38" s="37">
         <f>SUMPRODUCT(AM20:AM25,'Unit Economics'!$E$15:$E$20,Inputs!$H$57:$H$62)*AM37</f>
         <v/>
       </c>
-      <c r="AO38" s="35">
+      <c r="AO38" s="37">
         <f>SUM(D38:O38)</f>
         <v/>
       </c>
-      <c r="AP38" s="35">
+      <c r="AP38" s="37">
         <f>SUM(P38:AA38)</f>
         <v/>
       </c>
-      <c r="AQ38" s="35">
+      <c r="AQ38" s="37">
         <f>SUM(AB38:AM38)</f>
         <v/>
       </c>
@@ -13858,159 +14059,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="37">
         <f>D34*Inputs!$B$13*Inputs!$B$14*D37</f>
         <v/>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="37">
         <f>E34*Inputs!$B$13*Inputs!$B$14*E37</f>
         <v/>
       </c>
-      <c r="F39" s="35">
+      <c r="F39" s="37">
         <f>F34*Inputs!$B$13*Inputs!$B$14*F37</f>
         <v/>
       </c>
-      <c r="G39" s="35">
+      <c r="G39" s="37">
         <f>G34*Inputs!$B$13*Inputs!$B$14*G37</f>
         <v/>
       </c>
-      <c r="H39" s="35">
+      <c r="H39" s="37">
         <f>H34*Inputs!$B$13*Inputs!$B$14*H37</f>
         <v/>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="37">
         <f>I34*Inputs!$B$13*Inputs!$B$14*I37</f>
         <v/>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="37">
         <f>J34*Inputs!$B$13*Inputs!$B$14*J37</f>
         <v/>
       </c>
-      <c r="K39" s="35">
+      <c r="K39" s="37">
         <f>K34*Inputs!$B$13*Inputs!$B$14*K37</f>
         <v/>
       </c>
-      <c r="L39" s="35">
+      <c r="L39" s="37">
         <f>L34*Inputs!$B$13*Inputs!$B$14*L37</f>
         <v/>
       </c>
-      <c r="M39" s="35">
+      <c r="M39" s="37">
         <f>M34*Inputs!$B$13*Inputs!$B$14*M37</f>
         <v/>
       </c>
-      <c r="N39" s="35">
+      <c r="N39" s="37">
         <f>N34*Inputs!$B$13*Inputs!$B$14*N37</f>
         <v/>
       </c>
-      <c r="O39" s="35">
+      <c r="O39" s="37">
         <f>O34*Inputs!$B$13*Inputs!$B$14*O37</f>
         <v/>
       </c>
-      <c r="P39" s="35">
+      <c r="P39" s="37">
         <f>P34*Inputs!$B$13*Inputs!$B$14*P37</f>
         <v/>
       </c>
-      <c r="Q39" s="35">
+      <c r="Q39" s="37">
         <f>Q34*Inputs!$B$13*Inputs!$B$14*Q37</f>
         <v/>
       </c>
-      <c r="R39" s="35">
+      <c r="R39" s="37">
         <f>R34*Inputs!$B$13*Inputs!$B$14*R37</f>
         <v/>
       </c>
-      <c r="S39" s="35">
+      <c r="S39" s="37">
         <f>S34*Inputs!$B$13*Inputs!$B$14*S37</f>
         <v/>
       </c>
-      <c r="T39" s="35">
+      <c r="T39" s="37">
         <f>T34*Inputs!$B$13*Inputs!$B$14*T37</f>
         <v/>
       </c>
-      <c r="U39" s="35">
+      <c r="U39" s="37">
         <f>U34*Inputs!$B$13*Inputs!$B$14*U37</f>
         <v/>
       </c>
-      <c r="V39" s="35">
+      <c r="V39" s="37">
         <f>V34*Inputs!$B$13*Inputs!$B$14*V37</f>
         <v/>
       </c>
-      <c r="W39" s="35">
+      <c r="W39" s="37">
         <f>W34*Inputs!$B$13*Inputs!$B$14*W37</f>
         <v/>
       </c>
-      <c r="X39" s="35">
+      <c r="X39" s="37">
         <f>X34*Inputs!$B$13*Inputs!$B$14*X37</f>
         <v/>
       </c>
-      <c r="Y39" s="35">
+      <c r="Y39" s="37">
         <f>Y34*Inputs!$B$13*Inputs!$B$14*Y37</f>
         <v/>
       </c>
-      <c r="Z39" s="35">
+      <c r="Z39" s="37">
         <f>Z34*Inputs!$B$13*Inputs!$B$14*Z37</f>
         <v/>
       </c>
-      <c r="AA39" s="35">
+      <c r="AA39" s="37">
         <f>AA34*Inputs!$B$13*Inputs!$B$14*AA37</f>
         <v/>
       </c>
-      <c r="AB39" s="35">
+      <c r="AB39" s="37">
         <f>AB34*Inputs!$B$13*Inputs!$B$14*AB37</f>
         <v/>
       </c>
-      <c r="AC39" s="35">
+      <c r="AC39" s="37">
         <f>AC34*Inputs!$B$13*Inputs!$B$14*AC37</f>
         <v/>
       </c>
-      <c r="AD39" s="35">
+      <c r="AD39" s="37">
         <f>AD34*Inputs!$B$13*Inputs!$B$14*AD37</f>
         <v/>
       </c>
-      <c r="AE39" s="35">
+      <c r="AE39" s="37">
         <f>AE34*Inputs!$B$13*Inputs!$B$14*AE37</f>
         <v/>
       </c>
-      <c r="AF39" s="35">
+      <c r="AF39" s="37">
         <f>AF34*Inputs!$B$13*Inputs!$B$14*AF37</f>
         <v/>
       </c>
-      <c r="AG39" s="35">
+      <c r="AG39" s="37">
         <f>AG34*Inputs!$B$13*Inputs!$B$14*AG37</f>
         <v/>
       </c>
-      <c r="AH39" s="35">
+      <c r="AH39" s="37">
         <f>AH34*Inputs!$B$13*Inputs!$B$14*AH37</f>
         <v/>
       </c>
-      <c r="AI39" s="35">
+      <c r="AI39" s="37">
         <f>AI34*Inputs!$B$13*Inputs!$B$14*AI37</f>
         <v/>
       </c>
-      <c r="AJ39" s="35">
+      <c r="AJ39" s="37">
         <f>AJ34*Inputs!$B$13*Inputs!$B$14*AJ37</f>
         <v/>
       </c>
-      <c r="AK39" s="35">
+      <c r="AK39" s="37">
         <f>AK34*Inputs!$B$13*Inputs!$B$14*AK37</f>
         <v/>
       </c>
-      <c r="AL39" s="35">
+      <c r="AL39" s="37">
         <f>AL34*Inputs!$B$13*Inputs!$B$14*AL37</f>
         <v/>
       </c>
-      <c r="AM39" s="35">
+      <c r="AM39" s="37">
         <f>AM34*Inputs!$B$13*Inputs!$B$14*AM37</f>
         <v/>
       </c>
-      <c r="AO39" s="35">
+      <c r="AO39" s="37">
         <f>SUM(D39:O39)</f>
         <v/>
       </c>
-      <c r="AP39" s="35">
+      <c r="AP39" s="37">
         <f>SUM(P39:AA39)</f>
         <v/>
       </c>
-      <c r="AQ39" s="35">
+      <c r="AQ39" s="37">
         <f>SUM(AB39:AM39)</f>
         <v/>
       </c>
@@ -14026,159 +14227,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D40" s="38">
+      <c r="D40" s="40">
         <f>D38+D39</f>
         <v/>
       </c>
-      <c r="E40" s="38">
+      <c r="E40" s="40">
         <f>E38+E39</f>
         <v/>
       </c>
-      <c r="F40" s="38">
+      <c r="F40" s="40">
         <f>F38+F39</f>
         <v/>
       </c>
-      <c r="G40" s="38">
+      <c r="G40" s="40">
         <f>G38+G39</f>
         <v/>
       </c>
-      <c r="H40" s="38">
+      <c r="H40" s="40">
         <f>H38+H39</f>
         <v/>
       </c>
-      <c r="I40" s="38">
+      <c r="I40" s="40">
         <f>I38+I39</f>
         <v/>
       </c>
-      <c r="J40" s="38">
+      <c r="J40" s="40">
         <f>J38+J39</f>
         <v/>
       </c>
-      <c r="K40" s="38">
+      <c r="K40" s="40">
         <f>K38+K39</f>
         <v/>
       </c>
-      <c r="L40" s="38">
+      <c r="L40" s="40">
         <f>L38+L39</f>
         <v/>
       </c>
-      <c r="M40" s="38">
+      <c r="M40" s="40">
         <f>M38+M39</f>
         <v/>
       </c>
-      <c r="N40" s="38">
+      <c r="N40" s="40">
         <f>N38+N39</f>
         <v/>
       </c>
-      <c r="O40" s="38">
+      <c r="O40" s="40">
         <f>O38+O39</f>
         <v/>
       </c>
-      <c r="P40" s="38">
+      <c r="P40" s="40">
         <f>P38+P39</f>
         <v/>
       </c>
-      <c r="Q40" s="38">
+      <c r="Q40" s="40">
         <f>Q38+Q39</f>
         <v/>
       </c>
-      <c r="R40" s="38">
+      <c r="R40" s="40">
         <f>R38+R39</f>
         <v/>
       </c>
-      <c r="S40" s="38">
+      <c r="S40" s="40">
         <f>S38+S39</f>
         <v/>
       </c>
-      <c r="T40" s="38">
+      <c r="T40" s="40">
         <f>T38+T39</f>
         <v/>
       </c>
-      <c r="U40" s="38">
+      <c r="U40" s="40">
         <f>U38+U39</f>
         <v/>
       </c>
-      <c r="V40" s="38">
+      <c r="V40" s="40">
         <f>V38+V39</f>
         <v/>
       </c>
-      <c r="W40" s="38">
+      <c r="W40" s="40">
         <f>W38+W39</f>
         <v/>
       </c>
-      <c r="X40" s="38">
+      <c r="X40" s="40">
         <f>X38+X39</f>
         <v/>
       </c>
-      <c r="Y40" s="38">
+      <c r="Y40" s="40">
         <f>Y38+Y39</f>
         <v/>
       </c>
-      <c r="Z40" s="38">
+      <c r="Z40" s="40">
         <f>Z38+Z39</f>
         <v/>
       </c>
-      <c r="AA40" s="38">
+      <c r="AA40" s="40">
         <f>AA38+AA39</f>
         <v/>
       </c>
-      <c r="AB40" s="38">
+      <c r="AB40" s="40">
         <f>AB38+AB39</f>
         <v/>
       </c>
-      <c r="AC40" s="38">
+      <c r="AC40" s="40">
         <f>AC38+AC39</f>
         <v/>
       </c>
-      <c r="AD40" s="38">
+      <c r="AD40" s="40">
         <f>AD38+AD39</f>
         <v/>
       </c>
-      <c r="AE40" s="38">
+      <c r="AE40" s="40">
         <f>AE38+AE39</f>
         <v/>
       </c>
-      <c r="AF40" s="38">
+      <c r="AF40" s="40">
         <f>AF38+AF39</f>
         <v/>
       </c>
-      <c r="AG40" s="38">
+      <c r="AG40" s="40">
         <f>AG38+AG39</f>
         <v/>
       </c>
-      <c r="AH40" s="38">
+      <c r="AH40" s="40">
         <f>AH38+AH39</f>
         <v/>
       </c>
-      <c r="AI40" s="38">
+      <c r="AI40" s="40">
         <f>AI38+AI39</f>
         <v/>
       </c>
-      <c r="AJ40" s="38">
+      <c r="AJ40" s="40">
         <f>AJ38+AJ39</f>
         <v/>
       </c>
-      <c r="AK40" s="38">
+      <c r="AK40" s="40">
         <f>AK38+AK39</f>
         <v/>
       </c>
-      <c r="AL40" s="38">
+      <c r="AL40" s="40">
         <f>AL38+AL39</f>
         <v/>
       </c>
-      <c r="AM40" s="38">
+      <c r="AM40" s="40">
         <f>AM38+AM39</f>
         <v/>
       </c>
-      <c r="AO40" s="38">
+      <c r="AO40" s="40">
         <f>SUM(D40:O40)</f>
         <v/>
       </c>
-      <c r="AP40" s="38">
+      <c r="AP40" s="40">
         <f>SUM(P40:AA40)</f>
         <v/>
       </c>
-      <c r="AQ40" s="38">
+      <c r="AQ40" s="40">
         <f>SUM(AB40:AM40)</f>
         <v/>
       </c>
@@ -14194,162 +14395,162 @@
           <t>#</t>
         </is>
       </c>
-      <c r="C41" s="35" t="n">
+      <c r="C41" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="35">
+      <c r="D41" s="37">
         <f>C41+D40</f>
         <v/>
       </c>
-      <c r="E41" s="35">
+      <c r="E41" s="37">
         <f>D41+E40</f>
         <v/>
       </c>
-      <c r="F41" s="35">
+      <c r="F41" s="37">
         <f>E41+F40</f>
         <v/>
       </c>
-      <c r="G41" s="35">
+      <c r="G41" s="37">
         <f>F41+G40</f>
         <v/>
       </c>
-      <c r="H41" s="35">
+      <c r="H41" s="37">
         <f>G41+H40</f>
         <v/>
       </c>
-      <c r="I41" s="35">
+      <c r="I41" s="37">
         <f>H41+I40</f>
         <v/>
       </c>
-      <c r="J41" s="35">
+      <c r="J41" s="37">
         <f>I41+J40</f>
         <v/>
       </c>
-      <c r="K41" s="35">
+      <c r="K41" s="37">
         <f>J41+K40</f>
         <v/>
       </c>
-      <c r="L41" s="35">
+      <c r="L41" s="37">
         <f>K41+L40</f>
         <v/>
       </c>
-      <c r="M41" s="35">
+      <c r="M41" s="37">
         <f>L41+M40</f>
         <v/>
       </c>
-      <c r="N41" s="35">
+      <c r="N41" s="37">
         <f>M41+N40</f>
         <v/>
       </c>
-      <c r="O41" s="35">
+      <c r="O41" s="37">
         <f>N41+O40</f>
         <v/>
       </c>
-      <c r="P41" s="35">
+      <c r="P41" s="37">
         <f>O41+P40</f>
         <v/>
       </c>
-      <c r="Q41" s="35">
+      <c r="Q41" s="37">
         <f>P41+Q40</f>
         <v/>
       </c>
-      <c r="R41" s="35">
+      <c r="R41" s="37">
         <f>Q41+R40</f>
         <v/>
       </c>
-      <c r="S41" s="35">
+      <c r="S41" s="37">
         <f>R41+S40</f>
         <v/>
       </c>
-      <c r="T41" s="35">
+      <c r="T41" s="37">
         <f>S41+T40</f>
         <v/>
       </c>
-      <c r="U41" s="35">
+      <c r="U41" s="37">
         <f>T41+U40</f>
         <v/>
       </c>
-      <c r="V41" s="35">
+      <c r="V41" s="37">
         <f>U41+V40</f>
         <v/>
       </c>
-      <c r="W41" s="35">
+      <c r="W41" s="37">
         <f>V41+W40</f>
         <v/>
       </c>
-      <c r="X41" s="35">
+      <c r="X41" s="37">
         <f>W41+X40</f>
         <v/>
       </c>
-      <c r="Y41" s="35">
+      <c r="Y41" s="37">
         <f>X41+Y40</f>
         <v/>
       </c>
-      <c r="Z41" s="35">
+      <c r="Z41" s="37">
         <f>Y41+Z40</f>
         <v/>
       </c>
-      <c r="AA41" s="35">
+      <c r="AA41" s="37">
         <f>Z41+AA40</f>
         <v/>
       </c>
-      <c r="AB41" s="35">
+      <c r="AB41" s="37">
         <f>AA41+AB40</f>
         <v/>
       </c>
-      <c r="AC41" s="35">
+      <c r="AC41" s="37">
         <f>AB41+AC40</f>
         <v/>
       </c>
-      <c r="AD41" s="35">
+      <c r="AD41" s="37">
         <f>AC41+AD40</f>
         <v/>
       </c>
-      <c r="AE41" s="35">
+      <c r="AE41" s="37">
         <f>AD41+AE40</f>
         <v/>
       </c>
-      <c r="AF41" s="35">
+      <c r="AF41" s="37">
         <f>AE41+AF40</f>
         <v/>
       </c>
-      <c r="AG41" s="35">
+      <c r="AG41" s="37">
         <f>AF41+AG40</f>
         <v/>
       </c>
-      <c r="AH41" s="35">
+      <c r="AH41" s="37">
         <f>AG41+AH40</f>
         <v/>
       </c>
-      <c r="AI41" s="35">
+      <c r="AI41" s="37">
         <f>AH41+AI40</f>
         <v/>
       </c>
-      <c r="AJ41" s="35">
+      <c r="AJ41" s="37">
         <f>AI41+AJ40</f>
         <v/>
       </c>
-      <c r="AK41" s="35">
+      <c r="AK41" s="37">
         <f>AJ41+AK40</f>
         <v/>
       </c>
-      <c r="AL41" s="35">
+      <c r="AL41" s="37">
         <f>AK41+AL40</f>
         <v/>
       </c>
-      <c r="AM41" s="35">
+      <c r="AM41" s="37">
         <f>AL41+AM40</f>
         <v/>
       </c>
-      <c r="AO41" s="35">
+      <c r="AO41" s="37">
         <f>O41</f>
         <v/>
       </c>
-      <c r="AP41" s="35">
+      <c r="AP41" s="37">
         <f>AA41</f>
         <v/>
       </c>
-      <c r="AQ41" s="35">
+      <c r="AQ41" s="37">
         <f>AM41</f>
         <v/>
       </c>
@@ -14365,159 +14566,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D42" s="35">
+      <c r="D42" s="37">
         <f>C41*Inputs!$B$32/12*Scenarios!$B$9*D9</f>
         <v/>
       </c>
-      <c r="E42" s="35">
+      <c r="E42" s="37">
         <f>D41*Inputs!$B$32/12*Scenarios!$B$9*E9</f>
         <v/>
       </c>
-      <c r="F42" s="35">
+      <c r="F42" s="37">
         <f>E41*Inputs!$B$32/12*Scenarios!$B$9*F9</f>
         <v/>
       </c>
-      <c r="G42" s="35">
+      <c r="G42" s="37">
         <f>F41*Inputs!$B$32/12*Scenarios!$B$9*G9</f>
         <v/>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="37">
         <f>G41*Inputs!$B$32/12*Scenarios!$B$9*H9</f>
         <v/>
       </c>
-      <c r="I42" s="35">
+      <c r="I42" s="37">
         <f>H41*Inputs!$B$32/12*Scenarios!$B$9*I9</f>
         <v/>
       </c>
-      <c r="J42" s="35">
+      <c r="J42" s="37">
         <f>I41*Inputs!$B$32/12*Scenarios!$B$9*J9</f>
         <v/>
       </c>
-      <c r="K42" s="35">
+      <c r="K42" s="37">
         <f>J41*Inputs!$B$32/12*Scenarios!$B$9*K9</f>
         <v/>
       </c>
-      <c r="L42" s="35">
+      <c r="L42" s="37">
         <f>K41*Inputs!$B$32/12*Scenarios!$B$9*L9</f>
         <v/>
       </c>
-      <c r="M42" s="35">
+      <c r="M42" s="37">
         <f>L41*Inputs!$B$32/12*Scenarios!$B$9*M9</f>
         <v/>
       </c>
-      <c r="N42" s="35">
+      <c r="N42" s="37">
         <f>M41*Inputs!$B$32/12*Scenarios!$B$9*N9</f>
         <v/>
       </c>
-      <c r="O42" s="35">
+      <c r="O42" s="37">
         <f>N41*Inputs!$B$32/12*Scenarios!$B$9*O9</f>
         <v/>
       </c>
-      <c r="P42" s="35">
+      <c r="P42" s="37">
         <f>O41*Inputs!$B$32/12*Scenarios!$B$9*P9</f>
         <v/>
       </c>
-      <c r="Q42" s="35">
+      <c r="Q42" s="37">
         <f>P41*Inputs!$B$32/12*Scenarios!$B$9*Q9</f>
         <v/>
       </c>
-      <c r="R42" s="35">
+      <c r="R42" s="37">
         <f>Q41*Inputs!$B$32/12*Scenarios!$B$9*R9</f>
         <v/>
       </c>
-      <c r="S42" s="35">
+      <c r="S42" s="37">
         <f>R41*Inputs!$B$32/12*Scenarios!$B$9*S9</f>
         <v/>
       </c>
-      <c r="T42" s="35">
+      <c r="T42" s="37">
         <f>S41*Inputs!$B$32/12*Scenarios!$B$9*T9</f>
         <v/>
       </c>
-      <c r="U42" s="35">
+      <c r="U42" s="37">
         <f>T41*Inputs!$B$32/12*Scenarios!$B$9*U9</f>
         <v/>
       </c>
-      <c r="V42" s="35">
+      <c r="V42" s="37">
         <f>U41*Inputs!$B$32/12*Scenarios!$B$9*V9</f>
         <v/>
       </c>
-      <c r="W42" s="35">
+      <c r="W42" s="37">
         <f>V41*Inputs!$B$32/12*Scenarios!$B$9*W9</f>
         <v/>
       </c>
-      <c r="X42" s="35">
+      <c r="X42" s="37">
         <f>W41*Inputs!$B$32/12*Scenarios!$B$9*X9</f>
         <v/>
       </c>
-      <c r="Y42" s="35">
+      <c r="Y42" s="37">
         <f>X41*Inputs!$B$32/12*Scenarios!$B$9*Y9</f>
         <v/>
       </c>
-      <c r="Z42" s="35">
+      <c r="Z42" s="37">
         <f>Y41*Inputs!$B$32/12*Scenarios!$B$9*Z9</f>
         <v/>
       </c>
-      <c r="AA42" s="35">
+      <c r="AA42" s="37">
         <f>Z41*Inputs!$B$32/12*Scenarios!$B$9*AA9</f>
         <v/>
       </c>
-      <c r="AB42" s="35">
+      <c r="AB42" s="37">
         <f>AA41*Inputs!$B$32/12*Scenarios!$B$9*AB9</f>
         <v/>
       </c>
-      <c r="AC42" s="35">
+      <c r="AC42" s="37">
         <f>AB41*Inputs!$B$32/12*Scenarios!$B$9*AC9</f>
         <v/>
       </c>
-      <c r="AD42" s="35">
+      <c r="AD42" s="37">
         <f>AC41*Inputs!$B$32/12*Scenarios!$B$9*AD9</f>
         <v/>
       </c>
-      <c r="AE42" s="35">
+      <c r="AE42" s="37">
         <f>AD41*Inputs!$B$32/12*Scenarios!$B$9*AE9</f>
         <v/>
       </c>
-      <c r="AF42" s="35">
+      <c r="AF42" s="37">
         <f>AE41*Inputs!$B$32/12*Scenarios!$B$9*AF9</f>
         <v/>
       </c>
-      <c r="AG42" s="35">
+      <c r="AG42" s="37">
         <f>AF41*Inputs!$B$32/12*Scenarios!$B$9*AG9</f>
         <v/>
       </c>
-      <c r="AH42" s="35">
+      <c r="AH42" s="37">
         <f>AG41*Inputs!$B$32/12*Scenarios!$B$9*AH9</f>
         <v/>
       </c>
-      <c r="AI42" s="35">
+      <c r="AI42" s="37">
         <f>AH41*Inputs!$B$32/12*Scenarios!$B$9*AI9</f>
         <v/>
       </c>
-      <c r="AJ42" s="35">
+      <c r="AJ42" s="37">
         <f>AI41*Inputs!$B$32/12*Scenarios!$B$9*AJ9</f>
         <v/>
       </c>
-      <c r="AK42" s="35">
+      <c r="AK42" s="37">
         <f>AJ41*Inputs!$B$32/12*Scenarios!$B$9*AK9</f>
         <v/>
       </c>
-      <c r="AL42" s="35">
+      <c r="AL42" s="37">
         <f>AK41*Inputs!$B$32/12*Scenarios!$B$9*AL9</f>
         <v/>
       </c>
-      <c r="AM42" s="35">
+      <c r="AM42" s="37">
         <f>AL41*Inputs!$B$32/12*Scenarios!$B$9*AM9</f>
         <v/>
       </c>
-      <c r="AO42" s="35">
+      <c r="AO42" s="37">
         <f>SUM(D42:O42)</f>
         <v/>
       </c>
-      <c r="AP42" s="35">
+      <c r="AP42" s="37">
         <f>SUM(P42:AA42)</f>
         <v/>
       </c>
-      <c r="AQ42" s="35">
+      <c r="AQ42" s="37">
         <f>SUM(AB42:AM42)</f>
         <v/>
       </c>
@@ -14533,159 +14734,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D43" s="38">
+      <c r="D43" s="40">
         <f>D40+D42</f>
         <v/>
       </c>
-      <c r="E43" s="38">
+      <c r="E43" s="40">
         <f>E40+E42</f>
         <v/>
       </c>
-      <c r="F43" s="38">
+      <c r="F43" s="40">
         <f>F40+F42</f>
         <v/>
       </c>
-      <c r="G43" s="38">
+      <c r="G43" s="40">
         <f>G40+G42</f>
         <v/>
       </c>
-      <c r="H43" s="38">
+      <c r="H43" s="40">
         <f>H40+H42</f>
         <v/>
       </c>
-      <c r="I43" s="38">
+      <c r="I43" s="40">
         <f>I40+I42</f>
         <v/>
       </c>
-      <c r="J43" s="38">
+      <c r="J43" s="40">
         <f>J40+J42</f>
         <v/>
       </c>
-      <c r="K43" s="38">
+      <c r="K43" s="40">
         <f>K40+K42</f>
         <v/>
       </c>
-      <c r="L43" s="38">
+      <c r="L43" s="40">
         <f>L40+L42</f>
         <v/>
       </c>
-      <c r="M43" s="38">
+      <c r="M43" s="40">
         <f>M40+M42</f>
         <v/>
       </c>
-      <c r="N43" s="38">
+      <c r="N43" s="40">
         <f>N40+N42</f>
         <v/>
       </c>
-      <c r="O43" s="38">
+      <c r="O43" s="40">
         <f>O40+O42</f>
         <v/>
       </c>
-      <c r="P43" s="38">
+      <c r="P43" s="40">
         <f>P40+P42</f>
         <v/>
       </c>
-      <c r="Q43" s="38">
+      <c r="Q43" s="40">
         <f>Q40+Q42</f>
         <v/>
       </c>
-      <c r="R43" s="38">
+      <c r="R43" s="40">
         <f>R40+R42</f>
         <v/>
       </c>
-      <c r="S43" s="38">
+      <c r="S43" s="40">
         <f>S40+S42</f>
         <v/>
       </c>
-      <c r="T43" s="38">
+      <c r="T43" s="40">
         <f>T40+T42</f>
         <v/>
       </c>
-      <c r="U43" s="38">
+      <c r="U43" s="40">
         <f>U40+U42</f>
         <v/>
       </c>
-      <c r="V43" s="38">
+      <c r="V43" s="40">
         <f>V40+V42</f>
         <v/>
       </c>
-      <c r="W43" s="38">
+      <c r="W43" s="40">
         <f>W40+W42</f>
         <v/>
       </c>
-      <c r="X43" s="38">
+      <c r="X43" s="40">
         <f>X40+X42</f>
         <v/>
       </c>
-      <c r="Y43" s="38">
+      <c r="Y43" s="40">
         <f>Y40+Y42</f>
         <v/>
       </c>
-      <c r="Z43" s="38">
+      <c r="Z43" s="40">
         <f>Z40+Z42</f>
         <v/>
       </c>
-      <c r="AA43" s="38">
+      <c r="AA43" s="40">
         <f>AA40+AA42</f>
         <v/>
       </c>
-      <c r="AB43" s="38">
+      <c r="AB43" s="40">
         <f>AB40+AB42</f>
         <v/>
       </c>
-      <c r="AC43" s="38">
+      <c r="AC43" s="40">
         <f>AC40+AC42</f>
         <v/>
       </c>
-      <c r="AD43" s="38">
+      <c r="AD43" s="40">
         <f>AD40+AD42</f>
         <v/>
       </c>
-      <c r="AE43" s="38">
+      <c r="AE43" s="40">
         <f>AE40+AE42</f>
         <v/>
       </c>
-      <c r="AF43" s="38">
+      <c r="AF43" s="40">
         <f>AF40+AF42</f>
         <v/>
       </c>
-      <c r="AG43" s="38">
+      <c r="AG43" s="40">
         <f>AG40+AG42</f>
         <v/>
       </c>
-      <c r="AH43" s="38">
+      <c r="AH43" s="40">
         <f>AH40+AH42</f>
         <v/>
       </c>
-      <c r="AI43" s="38">
+      <c r="AI43" s="40">
         <f>AI40+AI42</f>
         <v/>
       </c>
-      <c r="AJ43" s="38">
+      <c r="AJ43" s="40">
         <f>AJ40+AJ42</f>
         <v/>
       </c>
-      <c r="AK43" s="38">
+      <c r="AK43" s="40">
         <f>AK40+AK42</f>
         <v/>
       </c>
-      <c r="AL43" s="38">
+      <c r="AL43" s="40">
         <f>AL40+AL42</f>
         <v/>
       </c>
-      <c r="AM43" s="38">
+      <c r="AM43" s="40">
         <f>AM40+AM42</f>
         <v/>
       </c>
-      <c r="AO43" s="38">
+      <c r="AO43" s="40">
         <f>SUM(D43:O43)</f>
         <v/>
       </c>
-      <c r="AP43" s="38">
+      <c r="AP43" s="40">
         <f>SUM(P43:AA43)</f>
         <v/>
       </c>
-      <c r="AQ43" s="38">
+      <c r="AQ43" s="40">
         <f>SUM(AB43:AM43)</f>
         <v/>
       </c>
@@ -14701,162 +14902,162 @@
           <t>#</t>
         </is>
       </c>
-      <c r="C44" s="35" t="n">
+      <c r="C44" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="37">
         <f>D43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="37">
         <f>E43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="F44" s="35">
+      <c r="F44" s="37">
         <f>F43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="G44" s="35">
+      <c r="G44" s="37">
         <f>G43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="H44" s="35">
+      <c r="H44" s="37">
         <f>H43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="I44" s="35">
+      <c r="I44" s="37">
         <f>I43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="J44" s="35">
+      <c r="J44" s="37">
         <f>J43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="K44" s="35">
+      <c r="K44" s="37">
         <f>K43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="L44" s="35">
+      <c r="L44" s="37">
         <f>L43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="M44" s="35">
+      <c r="M44" s="37">
         <f>M43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="N44" s="35">
+      <c r="N44" s="37">
         <f>N43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="O44" s="35">
+      <c r="O44" s="37">
         <f>O43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="P44" s="35">
+      <c r="P44" s="37">
         <f>P43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="Q44" s="35">
+      <c r="Q44" s="37">
         <f>Q43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="R44" s="35">
+      <c r="R44" s="37">
         <f>R43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="S44" s="35">
+      <c r="S44" s="37">
         <f>S43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="T44" s="35">
+      <c r="T44" s="37">
         <f>T43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="U44" s="35">
+      <c r="U44" s="37">
         <f>U43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="V44" s="35">
+      <c r="V44" s="37">
         <f>V43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="W44" s="35">
+      <c r="W44" s="37">
         <f>W43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="X44" s="35">
+      <c r="X44" s="37">
         <f>X43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="Y44" s="35">
+      <c r="Y44" s="37">
         <f>Y43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="Z44" s="35">
+      <c r="Z44" s="37">
         <f>Z43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AA44" s="35">
+      <c r="AA44" s="37">
         <f>AA43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AB44" s="35">
+      <c r="AB44" s="37">
         <f>AB43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AC44" s="35">
+      <c r="AC44" s="37">
         <f>AC43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AD44" s="35">
+      <c r="AD44" s="37">
         <f>AD43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AE44" s="35">
+      <c r="AE44" s="37">
         <f>AE43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AF44" s="35">
+      <c r="AF44" s="37">
         <f>AF43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AG44" s="35">
+      <c r="AG44" s="37">
         <f>AG43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AH44" s="35">
+      <c r="AH44" s="37">
         <f>AH43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AI44" s="35">
+      <c r="AI44" s="37">
         <f>AI43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AJ44" s="35">
+      <c r="AJ44" s="37">
         <f>AJ43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AK44" s="35">
+      <c r="AK44" s="37">
         <f>AK43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AL44" s="35">
+      <c r="AL44" s="37">
         <f>AL43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AM44" s="35">
+      <c r="AM44" s="37">
         <f>AM43*Inputs!$B$9</f>
         <v/>
       </c>
-      <c r="AO44" s="35">
+      <c r="AO44" s="37">
         <f>SUM(D44:O44)</f>
         <v/>
       </c>
-      <c r="AP44" s="35">
+      <c r="AP44" s="37">
         <f>SUM(P44:AA44)</f>
         <v/>
       </c>
-      <c r="AQ44" s="35">
+      <c r="AQ44" s="37">
         <f>SUM(AB44:AM44)</f>
         <v/>
       </c>
@@ -15088,159 +15289,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D47" s="35">
+      <c r="D47" s="37">
         <f>D44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="E47" s="35">
+      <c r="E47" s="37">
         <f>E44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="F47" s="35">
+      <c r="F47" s="37">
         <f>F44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="G47" s="35">
+      <c r="G47" s="37">
         <f>G44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="H47" s="35">
+      <c r="H47" s="37">
         <f>H44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="I47" s="35">
+      <c r="I47" s="37">
         <f>I44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="J47" s="35">
+      <c r="J47" s="37">
         <f>J44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="K47" s="35">
+      <c r="K47" s="37">
         <f>K44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="L47" s="35">
+      <c r="L47" s="37">
         <f>L44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="M47" s="35">
+      <c r="M47" s="37">
         <f>M44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="N47" s="35">
+      <c r="N47" s="37">
         <f>N44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="O47" s="35">
+      <c r="O47" s="37">
         <f>O44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="P47" s="35">
+      <c r="P47" s="37">
         <f>P44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="Q47" s="35">
+      <c r="Q47" s="37">
         <f>Q44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="R47" s="35">
+      <c r="R47" s="37">
         <f>R44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="S47" s="35">
+      <c r="S47" s="37">
         <f>S44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="T47" s="35">
+      <c r="T47" s="37">
         <f>T44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="U47" s="35">
+      <c r="U47" s="37">
         <f>U44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="V47" s="35">
+      <c r="V47" s="37">
         <f>V44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="W47" s="35">
+      <c r="W47" s="37">
         <f>W44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="X47" s="35">
+      <c r="X47" s="37">
         <f>X44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="Y47" s="35">
+      <c r="Y47" s="37">
         <f>Y44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="Z47" s="35">
+      <c r="Z47" s="37">
         <f>Z44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AA47" s="35">
+      <c r="AA47" s="37">
         <f>AA44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AB47" s="35">
+      <c r="AB47" s="37">
         <f>AB44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AC47" s="35">
+      <c r="AC47" s="37">
         <f>AC44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AD47" s="35">
+      <c r="AD47" s="37">
         <f>AD44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AE47" s="35">
+      <c r="AE47" s="37">
         <f>AE44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AF47" s="35">
+      <c r="AF47" s="37">
         <f>AF44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AG47" s="35">
+      <c r="AG47" s="37">
         <f>AG44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AH47" s="35">
+      <c r="AH47" s="37">
         <f>AH44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AI47" s="35">
+      <c r="AI47" s="37">
         <f>AI44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AJ47" s="35">
+      <c r="AJ47" s="37">
         <f>AJ44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AK47" s="35">
+      <c r="AK47" s="37">
         <f>AK44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AL47" s="35">
+      <c r="AL47" s="37">
         <f>AL44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AM47" s="35">
+      <c r="AM47" s="37">
         <f>AM44*Inputs!$G$47</f>
         <v/>
       </c>
-      <c r="AO47" s="35">
+      <c r="AO47" s="37">
         <f>SUM(D47:O47)</f>
         <v/>
       </c>
-      <c r="AP47" s="35">
+      <c r="AP47" s="37">
         <f>SUM(P47:AA47)</f>
         <v/>
       </c>
-      <c r="AQ47" s="35">
+      <c r="AQ47" s="37">
         <f>SUM(AB47:AM47)</f>
         <v/>
       </c>
@@ -15255,159 +15456,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D48" s="35">
+      <c r="D48" s="37">
         <f>D44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="E48" s="35">
+      <c r="E48" s="37">
         <f>E44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="F48" s="35">
+      <c r="F48" s="37">
         <f>F44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="G48" s="35">
+      <c r="G48" s="37">
         <f>G44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="H48" s="35">
+      <c r="H48" s="37">
         <f>H44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="I48" s="35">
+      <c r="I48" s="37">
         <f>I44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="J48" s="35">
+      <c r="J48" s="37">
         <f>J44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="K48" s="35">
+      <c r="K48" s="37">
         <f>K44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="L48" s="35">
+      <c r="L48" s="37">
         <f>L44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="M48" s="35">
+      <c r="M48" s="37">
         <f>M44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="N48" s="35">
+      <c r="N48" s="37">
         <f>N44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="O48" s="35">
+      <c r="O48" s="37">
         <f>O44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="P48" s="35">
+      <c r="P48" s="37">
         <f>P44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="Q48" s="35">
+      <c r="Q48" s="37">
         <f>Q44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="R48" s="35">
+      <c r="R48" s="37">
         <f>R44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="S48" s="35">
+      <c r="S48" s="37">
         <f>S44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="T48" s="35">
+      <c r="T48" s="37">
         <f>T44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="U48" s="35">
+      <c r="U48" s="37">
         <f>U44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="V48" s="35">
+      <c r="V48" s="37">
         <f>V44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="W48" s="35">
+      <c r="W48" s="37">
         <f>W44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="X48" s="35">
+      <c r="X48" s="37">
         <f>X44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="Y48" s="35">
+      <c r="Y48" s="37">
         <f>Y44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="Z48" s="35">
+      <c r="Z48" s="37">
         <f>Z44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AA48" s="35">
+      <c r="AA48" s="37">
         <f>AA44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AB48" s="35">
+      <c r="AB48" s="37">
         <f>AB44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AC48" s="35">
+      <c r="AC48" s="37">
         <f>AC44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AD48" s="35">
+      <c r="AD48" s="37">
         <f>AD44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AE48" s="35">
+      <c r="AE48" s="37">
         <f>AE44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AF48" s="35">
+      <c r="AF48" s="37">
         <f>AF44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AG48" s="35">
+      <c r="AG48" s="37">
         <f>AG44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AH48" s="35">
+      <c r="AH48" s="37">
         <f>AH44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AI48" s="35">
+      <c r="AI48" s="37">
         <f>AI44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AJ48" s="35">
+      <c r="AJ48" s="37">
         <f>AJ44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AK48" s="35">
+      <c r="AK48" s="37">
         <f>AK44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AL48" s="35">
+      <c r="AL48" s="37">
         <f>AL44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AM48" s="35">
+      <c r="AM48" s="37">
         <f>AM44*Inputs!$G$48</f>
         <v/>
       </c>
-      <c r="AO48" s="35">
+      <c r="AO48" s="37">
         <f>SUM(D48:O48)</f>
         <v/>
       </c>
-      <c r="AP48" s="35">
+      <c r="AP48" s="37">
         <f>SUM(P48:AA48)</f>
         <v/>
       </c>
-      <c r="AQ48" s="35">
+      <c r="AQ48" s="37">
         <f>SUM(AB48:AM48)</f>
         <v/>
       </c>
@@ -15422,159 +15623,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D49" s="35">
+      <c r="D49" s="37">
         <f>D44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="E49" s="35">
+      <c r="E49" s="37">
         <f>E44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="F49" s="35">
+      <c r="F49" s="37">
         <f>F44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="G49" s="35">
+      <c r="G49" s="37">
         <f>G44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="H49" s="35">
+      <c r="H49" s="37">
         <f>H44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="I49" s="35">
+      <c r="I49" s="37">
         <f>I44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="J49" s="35">
+      <c r="J49" s="37">
         <f>J44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="K49" s="35">
+      <c r="K49" s="37">
         <f>K44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="L49" s="35">
+      <c r="L49" s="37">
         <f>L44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="M49" s="35">
+      <c r="M49" s="37">
         <f>M44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="N49" s="35">
+      <c r="N49" s="37">
         <f>N44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="O49" s="35">
+      <c r="O49" s="37">
         <f>O44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="P49" s="35">
+      <c r="P49" s="37">
         <f>P44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="Q49" s="35">
+      <c r="Q49" s="37">
         <f>Q44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="R49" s="35">
+      <c r="R49" s="37">
         <f>R44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="S49" s="35">
+      <c r="S49" s="37">
         <f>S44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="T49" s="35">
+      <c r="T49" s="37">
         <f>T44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="U49" s="35">
+      <c r="U49" s="37">
         <f>U44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="V49" s="35">
+      <c r="V49" s="37">
         <f>V44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="W49" s="35">
+      <c r="W49" s="37">
         <f>W44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="X49" s="35">
+      <c r="X49" s="37">
         <f>X44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="Y49" s="35">
+      <c r="Y49" s="37">
         <f>Y44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="Z49" s="35">
+      <c r="Z49" s="37">
         <f>Z44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AA49" s="35">
+      <c r="AA49" s="37">
         <f>AA44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AB49" s="35">
+      <c r="AB49" s="37">
         <f>AB44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AC49" s="35">
+      <c r="AC49" s="37">
         <f>AC44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AD49" s="35">
+      <c r="AD49" s="37">
         <f>AD44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AE49" s="35">
+      <c r="AE49" s="37">
         <f>AE44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AF49" s="35">
+      <c r="AF49" s="37">
         <f>AF44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AG49" s="35">
+      <c r="AG49" s="37">
         <f>AG44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AH49" s="35">
+      <c r="AH49" s="37">
         <f>AH44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AI49" s="35">
+      <c r="AI49" s="37">
         <f>AI44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AJ49" s="35">
+      <c r="AJ49" s="37">
         <f>AJ44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AK49" s="35">
+      <c r="AK49" s="37">
         <f>AK44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AL49" s="35">
+      <c r="AL49" s="37">
         <f>AL44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AM49" s="35">
+      <c r="AM49" s="37">
         <f>AM44*Inputs!$G$49</f>
         <v/>
       </c>
-      <c r="AO49" s="35">
+      <c r="AO49" s="37">
         <f>SUM(D49:O49)</f>
         <v/>
       </c>
-      <c r="AP49" s="35">
+      <c r="AP49" s="37">
         <f>SUM(P49:AA49)</f>
         <v/>
       </c>
-      <c r="AQ49" s="35">
+      <c r="AQ49" s="37">
         <f>SUM(AB49:AM49)</f>
         <v/>
       </c>
@@ -15589,159 +15790,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D50" s="35">
+      <c r="D50" s="37">
         <f>D44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="E50" s="35">
+      <c r="E50" s="37">
         <f>E44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="F50" s="35">
+      <c r="F50" s="37">
         <f>F44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="G50" s="35">
+      <c r="G50" s="37">
         <f>G44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="H50" s="35">
+      <c r="H50" s="37">
         <f>H44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="I50" s="35">
+      <c r="I50" s="37">
         <f>I44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="J50" s="35">
+      <c r="J50" s="37">
         <f>J44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="K50" s="35">
+      <c r="K50" s="37">
         <f>K44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="L50" s="35">
+      <c r="L50" s="37">
         <f>L44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="M50" s="35">
+      <c r="M50" s="37">
         <f>M44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="N50" s="35">
+      <c r="N50" s="37">
         <f>N44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="O50" s="35">
+      <c r="O50" s="37">
         <f>O44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="P50" s="35">
+      <c r="P50" s="37">
         <f>P44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="Q50" s="35">
+      <c r="Q50" s="37">
         <f>Q44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="R50" s="35">
+      <c r="R50" s="37">
         <f>R44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="S50" s="35">
+      <c r="S50" s="37">
         <f>S44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="T50" s="35">
+      <c r="T50" s="37">
         <f>T44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="U50" s="35">
+      <c r="U50" s="37">
         <f>U44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="V50" s="35">
+      <c r="V50" s="37">
         <f>V44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="W50" s="35">
+      <c r="W50" s="37">
         <f>W44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="X50" s="35">
+      <c r="X50" s="37">
         <f>X44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="Y50" s="35">
+      <c r="Y50" s="37">
         <f>Y44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="Z50" s="35">
+      <c r="Z50" s="37">
         <f>Z44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AA50" s="35">
+      <c r="AA50" s="37">
         <f>AA44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AB50" s="35">
+      <c r="AB50" s="37">
         <f>AB44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AC50" s="35">
+      <c r="AC50" s="37">
         <f>AC44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AD50" s="35">
+      <c r="AD50" s="37">
         <f>AD44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AE50" s="35">
+      <c r="AE50" s="37">
         <f>AE44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AF50" s="35">
+      <c r="AF50" s="37">
         <f>AF44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AG50" s="35">
+      <c r="AG50" s="37">
         <f>AG44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AH50" s="35">
+      <c r="AH50" s="37">
         <f>AH44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AI50" s="35">
+      <c r="AI50" s="37">
         <f>AI44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AJ50" s="35">
+      <c r="AJ50" s="37">
         <f>AJ44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AK50" s="35">
+      <c r="AK50" s="37">
         <f>AK44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AL50" s="35">
+      <c r="AL50" s="37">
         <f>AL44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AM50" s="35">
+      <c r="AM50" s="37">
         <f>AM44*Inputs!$G$50</f>
         <v/>
       </c>
-      <c r="AO50" s="35">
+      <c r="AO50" s="37">
         <f>SUM(D50:O50)</f>
         <v/>
       </c>
-      <c r="AP50" s="35">
+      <c r="AP50" s="37">
         <f>SUM(P50:AA50)</f>
         <v/>
       </c>
-      <c r="AQ50" s="35">
+      <c r="AQ50" s="37">
         <f>SUM(AB50:AM50)</f>
         <v/>
       </c>
@@ -15756,159 +15957,159 @@
           <t>#</t>
         </is>
       </c>
-      <c r="D51" s="35">
+      <c r="D51" s="37">
         <f>D44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="E51" s="35">
+      <c r="E51" s="37">
         <f>E44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="F51" s="35">
+      <c r="F51" s="37">
         <f>F44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="G51" s="35">
+      <c r="G51" s="37">
         <f>G44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="H51" s="35">
+      <c r="H51" s="37">
         <f>H44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="I51" s="35">
+      <c r="I51" s="37">
         <f>I44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="J51" s="35">
+      <c r="J51" s="37">
         <f>J44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="K51" s="35">
+      <c r="K51" s="37">
         <f>K44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="L51" s="35">
+      <c r="L51" s="37">
         <f>L44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="M51" s="35">
+      <c r="M51" s="37">
         <f>M44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="N51" s="35">
+      <c r="N51" s="37">
         <f>N44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="O51" s="35">
+      <c r="O51" s="37">
         <f>O44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="P51" s="35">
+      <c r="P51" s="37">
         <f>P44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="Q51" s="35">
+      <c r="Q51" s="37">
         <f>Q44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="R51" s="35">
+      <c r="R51" s="37">
         <f>R44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="S51" s="35">
+      <c r="S51" s="37">
         <f>S44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="T51" s="35">
+      <c r="T51" s="37">
         <f>T44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="U51" s="35">
+      <c r="U51" s="37">
         <f>U44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="V51" s="35">
+      <c r="V51" s="37">
         <f>V44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="W51" s="35">
+      <c r="W51" s="37">
         <f>W44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="X51" s="35">
+      <c r="X51" s="37">
         <f>X44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="Y51" s="35">
+      <c r="Y51" s="37">
         <f>Y44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="Z51" s="35">
+      <c r="Z51" s="37">
         <f>Z44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AA51" s="35">
+      <c r="AA51" s="37">
         <f>AA44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AB51" s="35">
+      <c r="AB51" s="37">
         <f>AB44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AC51" s="35">
+      <c r="AC51" s="37">
         <f>AC44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AD51" s="35">
+      <c r="AD51" s="37">
         <f>AD44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AE51" s="35">
+      <c r="AE51" s="37">
         <f>AE44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AF51" s="35">
+      <c r="AF51" s="37">
         <f>AF44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AG51" s="35">
+      <c r="AG51" s="37">
         <f>AG44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AH51" s="35">
+      <c r="AH51" s="37">
         <f>AH44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AI51" s="35">
+      <c r="AI51" s="37">
         <f>AI44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AJ51" s="35">
+      <c r="AJ51" s="37">
         <f>AJ44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AK51" s="35">
+      <c r="AK51" s="37">
         <f>AK44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AL51" s="35">
+      <c r="AL51" s="37">
         <f>AL44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AM51" s="35">
+      <c r="AM51" s="37">
         <f>AM44*Inputs!$G$51</f>
         <v/>
       </c>
-      <c r="AO51" s="35">
+      <c r="AO51" s="37">
         <f>SUM(D51:O51)</f>
         <v/>
       </c>
-      <c r="AP51" s="35">
+      <c r="AP51" s="37">
         <f>SUM(P51:AA51)</f>
         <v/>
       </c>
-      <c r="AQ51" s="35">
+      <c r="AQ51" s="37">
         <f>SUM(AB51:AM51)</f>
         <v/>
       </c>
@@ -17530,147 +17731,147 @@
         </is>
       </c>
       <c r="D63" s="15">
-        <f>D32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>D32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="E63" s="15">
-        <f>E32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>E32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="F63" s="15">
-        <f>F32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>F32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="G63" s="15">
-        <f>G32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>G32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="H63" s="15">
-        <f>H32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>H32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="I63" s="15">
-        <f>I32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>I32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="J63" s="15">
-        <f>J32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>J32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="K63" s="15">
-        <f>K32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>K32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="L63" s="15">
-        <f>L32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>L32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="M63" s="15">
-        <f>M32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>M32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="N63" s="15">
-        <f>N32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>N32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="O63" s="15">
-        <f>O32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>O32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="P63" s="15">
-        <f>P32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>P32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="Q63" s="15">
-        <f>Q32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>Q32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="R63" s="15">
-        <f>R32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>R32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="S63" s="15">
-        <f>S32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>S32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="T63" s="15">
-        <f>T32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>T32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="U63" s="15">
-        <f>U32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>U32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="V63" s="15">
-        <f>V32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>V32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="W63" s="15">
-        <f>W32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>W32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="X63" s="15">
-        <f>X32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>X32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="Y63" s="15">
-        <f>Y32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>Y32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="Z63" s="15">
-        <f>Z32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>Z32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AA63" s="15">
-        <f>AA32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AA32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AB63" s="15">
-        <f>AB32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AB32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AC63" s="15">
-        <f>AC32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AC32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AD63" s="15">
-        <f>AD32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AD32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AE63" s="15">
-        <f>AE32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AE32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AF63" s="15">
-        <f>AF32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AF32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AG63" s="15">
-        <f>AG32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AG32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AH63" s="15">
-        <f>AH32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AH32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AI63" s="15">
-        <f>AI32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AI32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AJ63" s="15">
-        <f>AJ32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AJ32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AK63" s="15">
-        <f>AK32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AK32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AL63" s="15">
-        <f>AL32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AL32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AM63" s="15">
-        <f>AM32*'Model Costs'!$B$37*Scenarios!$B$10*(1+Inputs!$B$42)</f>
+        <f>AM32*'Model Costs'!$B$46*Scenarios!$B$10*(1+Inputs!$B$42)</f>
         <v/>
       </c>
       <c r="AO63" s="15">
@@ -20814,147 +21015,147 @@
           <t>month</t>
         </is>
       </c>
-      <c r="D84" s="35">
+      <c r="D84" s="37">
         <f>IF(D77&gt;=0,D6,"")</f>
         <v/>
       </c>
-      <c r="E84" s="35">
+      <c r="E84" s="37">
         <f>IF(E77&gt;=0,E6,"")</f>
         <v/>
       </c>
-      <c r="F84" s="35">
+      <c r="F84" s="37">
         <f>IF(F77&gt;=0,F6,"")</f>
         <v/>
       </c>
-      <c r="G84" s="35">
+      <c r="G84" s="37">
         <f>IF(G77&gt;=0,G6,"")</f>
         <v/>
       </c>
-      <c r="H84" s="35">
+      <c r="H84" s="37">
         <f>IF(H77&gt;=0,H6,"")</f>
         <v/>
       </c>
-      <c r="I84" s="35">
+      <c r="I84" s="37">
         <f>IF(I77&gt;=0,I6,"")</f>
         <v/>
       </c>
-      <c r="J84" s="35">
+      <c r="J84" s="37">
         <f>IF(J77&gt;=0,J6,"")</f>
         <v/>
       </c>
-      <c r="K84" s="35">
+      <c r="K84" s="37">
         <f>IF(K77&gt;=0,K6,"")</f>
         <v/>
       </c>
-      <c r="L84" s="35">
+      <c r="L84" s="37">
         <f>IF(L77&gt;=0,L6,"")</f>
         <v/>
       </c>
-      <c r="M84" s="35">
+      <c r="M84" s="37">
         <f>IF(M77&gt;=0,M6,"")</f>
         <v/>
       </c>
-      <c r="N84" s="35">
+      <c r="N84" s="37">
         <f>IF(N77&gt;=0,N6,"")</f>
         <v/>
       </c>
-      <c r="O84" s="35">
+      <c r="O84" s="37">
         <f>IF(O77&gt;=0,O6,"")</f>
         <v/>
       </c>
-      <c r="P84" s="35">
+      <c r="P84" s="37">
         <f>IF(P77&gt;=0,P6,"")</f>
         <v/>
       </c>
-      <c r="Q84" s="35">
+      <c r="Q84" s="37">
         <f>IF(Q77&gt;=0,Q6,"")</f>
         <v/>
       </c>
-      <c r="R84" s="35">
+      <c r="R84" s="37">
         <f>IF(R77&gt;=0,R6,"")</f>
         <v/>
       </c>
-      <c r="S84" s="35">
+      <c r="S84" s="37">
         <f>IF(S77&gt;=0,S6,"")</f>
         <v/>
       </c>
-      <c r="T84" s="35">
+      <c r="T84" s="37">
         <f>IF(T77&gt;=0,T6,"")</f>
         <v/>
       </c>
-      <c r="U84" s="35">
+      <c r="U84" s="37">
         <f>IF(U77&gt;=0,U6,"")</f>
         <v/>
       </c>
-      <c r="V84" s="35">
+      <c r="V84" s="37">
         <f>IF(V77&gt;=0,V6,"")</f>
         <v/>
       </c>
-      <c r="W84" s="35">
+      <c r="W84" s="37">
         <f>IF(W77&gt;=0,W6,"")</f>
         <v/>
       </c>
-      <c r="X84" s="35">
+      <c r="X84" s="37">
         <f>IF(X77&gt;=0,X6,"")</f>
         <v/>
       </c>
-      <c r="Y84" s="35">
+      <c r="Y84" s="37">
         <f>IF(Y77&gt;=0,Y6,"")</f>
         <v/>
       </c>
-      <c r="Z84" s="35">
+      <c r="Z84" s="37">
         <f>IF(Z77&gt;=0,Z6,"")</f>
         <v/>
       </c>
-      <c r="AA84" s="35">
+      <c r="AA84" s="37">
         <f>IF(AA77&gt;=0,AA6,"")</f>
         <v/>
       </c>
-      <c r="AB84" s="35">
+      <c r="AB84" s="37">
         <f>IF(AB77&gt;=0,AB6,"")</f>
         <v/>
       </c>
-      <c r="AC84" s="35">
+      <c r="AC84" s="37">
         <f>IF(AC77&gt;=0,AC6,"")</f>
         <v/>
       </c>
-      <c r="AD84" s="35">
+      <c r="AD84" s="37">
         <f>IF(AD77&gt;=0,AD6,"")</f>
         <v/>
       </c>
-      <c r="AE84" s="35">
+      <c r="AE84" s="37">
         <f>IF(AE77&gt;=0,AE6,"")</f>
         <v/>
       </c>
-      <c r="AF84" s="35">
+      <c r="AF84" s="37">
         <f>IF(AF77&gt;=0,AF6,"")</f>
         <v/>
       </c>
-      <c r="AG84" s="35">
+      <c r="AG84" s="37">
         <f>IF(AG77&gt;=0,AG6,"")</f>
         <v/>
       </c>
-      <c r="AH84" s="35">
+      <c r="AH84" s="37">
         <f>IF(AH77&gt;=0,AH6,"")</f>
         <v/>
       </c>
-      <c r="AI84" s="35">
+      <c r="AI84" s="37">
         <f>IF(AI77&gt;=0,AI6,"")</f>
         <v/>
       </c>
-      <c r="AJ84" s="35">
+      <c r="AJ84" s="37">
         <f>IF(AJ77&gt;=0,AJ6,"")</f>
         <v/>
       </c>
-      <c r="AK84" s="35">
+      <c r="AK84" s="37">
         <f>IF(AK77&gt;=0,AK6,"")</f>
         <v/>
       </c>
-      <c r="AL84" s="35">
+      <c r="AL84" s="37">
         <f>IF(AL77&gt;=0,AL6,"")</f>
         <v/>
       </c>
-      <c r="AM84" s="35">
+      <c r="AM84" s="37">
         <f>IF(AM77&gt;=0,AM6,"")</f>
         <v/>
       </c>
@@ -20970,147 +21171,147 @@
           <t>month</t>
         </is>
       </c>
-      <c r="D85" s="35">
+      <c r="D85" s="37">
         <f>IF(MIN(D83:$AM83)&gt;=0,D6,"")</f>
         <v/>
       </c>
-      <c r="E85" s="35">
+      <c r="E85" s="37">
         <f>IF(MIN(E83:$AM83)&gt;=0,E6,"")</f>
         <v/>
       </c>
-      <c r="F85" s="35">
+      <c r="F85" s="37">
         <f>IF(MIN(F83:$AM83)&gt;=0,F6,"")</f>
         <v/>
       </c>
-      <c r="G85" s="35">
+      <c r="G85" s="37">
         <f>IF(MIN(G83:$AM83)&gt;=0,G6,"")</f>
         <v/>
       </c>
-      <c r="H85" s="35">
+      <c r="H85" s="37">
         <f>IF(MIN(H83:$AM83)&gt;=0,H6,"")</f>
         <v/>
       </c>
-      <c r="I85" s="35">
+      <c r="I85" s="37">
         <f>IF(MIN(I83:$AM83)&gt;=0,I6,"")</f>
         <v/>
       </c>
-      <c r="J85" s="35">
+      <c r="J85" s="37">
         <f>IF(MIN(J83:$AM83)&gt;=0,J6,"")</f>
         <v/>
       </c>
-      <c r="K85" s="35">
+      <c r="K85" s="37">
         <f>IF(MIN(K83:$AM83)&gt;=0,K6,"")</f>
         <v/>
       </c>
-      <c r="L85" s="35">
+      <c r="L85" s="37">
         <f>IF(MIN(L83:$AM83)&gt;=0,L6,"")</f>
         <v/>
       </c>
-      <c r="M85" s="35">
+      <c r="M85" s="37">
         <f>IF(MIN(M83:$AM83)&gt;=0,M6,"")</f>
         <v/>
       </c>
-      <c r="N85" s="35">
+      <c r="N85" s="37">
         <f>IF(MIN(N83:$AM83)&gt;=0,N6,"")</f>
         <v/>
       </c>
-      <c r="O85" s="35">
+      <c r="O85" s="37">
         <f>IF(MIN(O83:$AM83)&gt;=0,O6,"")</f>
         <v/>
       </c>
-      <c r="P85" s="35">
+      <c r="P85" s="37">
         <f>IF(MIN(P83:$AM83)&gt;=0,P6,"")</f>
         <v/>
       </c>
-      <c r="Q85" s="35">
+      <c r="Q85" s="37">
         <f>IF(MIN(Q83:$AM83)&gt;=0,Q6,"")</f>
         <v/>
       </c>
-      <c r="R85" s="35">
+      <c r="R85" s="37">
         <f>IF(MIN(R83:$AM83)&gt;=0,R6,"")</f>
         <v/>
       </c>
-      <c r="S85" s="35">
+      <c r="S85" s="37">
         <f>IF(MIN(S83:$AM83)&gt;=0,S6,"")</f>
         <v/>
       </c>
-      <c r="T85" s="35">
+      <c r="T85" s="37">
         <f>IF(MIN(T83:$AM83)&gt;=0,T6,"")</f>
         <v/>
       </c>
-      <c r="U85" s="35">
+      <c r="U85" s="37">
         <f>IF(MIN(U83:$AM83)&gt;=0,U6,"")</f>
         <v/>
       </c>
-      <c r="V85" s="35">
+      <c r="V85" s="37">
         <f>IF(MIN(V83:$AM83)&gt;=0,V6,"")</f>
         <v/>
       </c>
-      <c r="W85" s="35">
+      <c r="W85" s="37">
         <f>IF(MIN(W83:$AM83)&gt;=0,W6,"")</f>
         <v/>
       </c>
-      <c r="X85" s="35">
+      <c r="X85" s="37">
         <f>IF(MIN(X83:$AM83)&gt;=0,X6,"")</f>
         <v/>
       </c>
-      <c r="Y85" s="35">
+      <c r="Y85" s="37">
         <f>IF(MIN(Y83:$AM83)&gt;=0,Y6,"")</f>
         <v/>
       </c>
-      <c r="Z85" s="35">
+      <c r="Z85" s="37">
         <f>IF(MIN(Z83:$AM83)&gt;=0,Z6,"")</f>
         <v/>
       </c>
-      <c r="AA85" s="35">
+      <c r="AA85" s="37">
         <f>IF(MIN(AA83:$AM83)&gt;=0,AA6,"")</f>
         <v/>
       </c>
-      <c r="AB85" s="35">
+      <c r="AB85" s="37">
         <f>IF(MIN(AB83:$AM83)&gt;=0,AB6,"")</f>
         <v/>
       </c>
-      <c r="AC85" s="35">
+      <c r="AC85" s="37">
         <f>IF(MIN(AC83:$AM83)&gt;=0,AC6,"")</f>
         <v/>
       </c>
-      <c r="AD85" s="35">
+      <c r="AD85" s="37">
         <f>IF(MIN(AD83:$AM83)&gt;=0,AD6,"")</f>
         <v/>
       </c>
-      <c r="AE85" s="35">
+      <c r="AE85" s="37">
         <f>IF(MIN(AE83:$AM83)&gt;=0,AE6,"")</f>
         <v/>
       </c>
-      <c r="AF85" s="35">
+      <c r="AF85" s="37">
         <f>IF(MIN(AF83:$AM83)&gt;=0,AF6,"")</f>
         <v/>
       </c>
-      <c r="AG85" s="35">
+      <c r="AG85" s="37">
         <f>IF(MIN(AG83:$AM83)&gt;=0,AG6,"")</f>
         <v/>
       </c>
-      <c r="AH85" s="35">
+      <c r="AH85" s="37">
         <f>IF(MIN(AH83:$AM83)&gt;=0,AH6,"")</f>
         <v/>
       </c>
-      <c r="AI85" s="35">
+      <c r="AI85" s="37">
         <f>IF(MIN(AI83:$AM83)&gt;=0,AI6,"")</f>
         <v/>
       </c>
-      <c r="AJ85" s="35">
+      <c r="AJ85" s="37">
         <f>IF(MIN(AJ83:$AM83)&gt;=0,AJ6,"")</f>
         <v/>
       </c>
-      <c r="AK85" s="35">
+      <c r="AK85" s="37">
         <f>IF(MIN(AK83:$AM83)&gt;=0,AK6,"")</f>
         <v/>
       </c>
-      <c r="AL85" s="35">
+      <c r="AL85" s="37">
         <f>IF(MIN(AL83:$AM83)&gt;=0,AL6,"")</f>
         <v/>
       </c>
-      <c r="AM85" s="35">
+      <c r="AM85" s="37">
         <f>IF(MIN(AM83:$AM83)&gt;=0,AM6,"")</f>
         <v/>
       </c>
@@ -21126,147 +21327,147 @@
           <t>month</t>
         </is>
       </c>
-      <c r="D86" s="35">
+      <c r="D86" s="37">
         <f>IF(D79&gt;=0,D6,"")</f>
         <v/>
       </c>
-      <c r="E86" s="35">
+      <c r="E86" s="37">
         <f>IF(E79&gt;=0,E6,"")</f>
         <v/>
       </c>
-      <c r="F86" s="35">
+      <c r="F86" s="37">
         <f>IF(F79&gt;=0,F6,"")</f>
         <v/>
       </c>
-      <c r="G86" s="35">
+      <c r="G86" s="37">
         <f>IF(G79&gt;=0,G6,"")</f>
         <v/>
       </c>
-      <c r="H86" s="35">
+      <c r="H86" s="37">
         <f>IF(H79&gt;=0,H6,"")</f>
         <v/>
       </c>
-      <c r="I86" s="35">
+      <c r="I86" s="37">
         <f>IF(I79&gt;=0,I6,"")</f>
         <v/>
       </c>
-      <c r="J86" s="35">
+      <c r="J86" s="37">
         <f>IF(J79&gt;=0,J6,"")</f>
         <v/>
       </c>
-      <c r="K86" s="35">
+      <c r="K86" s="37">
         <f>IF(K79&gt;=0,K6,"")</f>
         <v/>
       </c>
-      <c r="L86" s="35">
+      <c r="L86" s="37">
         <f>IF(L79&gt;=0,L6,"")</f>
         <v/>
       </c>
-      <c r="M86" s="35">
+      <c r="M86" s="37">
         <f>IF(M79&gt;=0,M6,"")</f>
         <v/>
       </c>
-      <c r="N86" s="35">
+      <c r="N86" s="37">
         <f>IF(N79&gt;=0,N6,"")</f>
         <v/>
       </c>
-      <c r="O86" s="35">
+      <c r="O86" s="37">
         <f>IF(O79&gt;=0,O6,"")</f>
         <v/>
       </c>
-      <c r="P86" s="35">
+      <c r="P86" s="37">
         <f>IF(P79&gt;=0,P6,"")</f>
         <v/>
       </c>
-      <c r="Q86" s="35">
+      <c r="Q86" s="37">
         <f>IF(Q79&gt;=0,Q6,"")</f>
         <v/>
       </c>
-      <c r="R86" s="35">
+      <c r="R86" s="37">
         <f>IF(R79&gt;=0,R6,"")</f>
         <v/>
       </c>
-      <c r="S86" s="35">
+      <c r="S86" s="37">
         <f>IF(S79&gt;=0,S6,"")</f>
         <v/>
       </c>
-      <c r="T86" s="35">
+      <c r="T86" s="37">
         <f>IF(T79&gt;=0,T6,"")</f>
         <v/>
       </c>
-      <c r="U86" s="35">
+      <c r="U86" s="37">
         <f>IF(U79&gt;=0,U6,"")</f>
         <v/>
       </c>
-      <c r="V86" s="35">
+      <c r="V86" s="37">
         <f>IF(V79&gt;=0,V6,"")</f>
         <v/>
       </c>
-      <c r="W86" s="35">
+      <c r="W86" s="37">
         <f>IF(W79&gt;=0,W6,"")</f>
         <v/>
       </c>
-      <c r="X86" s="35">
+      <c r="X86" s="37">
         <f>IF(X79&gt;=0,X6,"")</f>
         <v/>
       </c>
-      <c r="Y86" s="35">
+      <c r="Y86" s="37">
         <f>IF(Y79&gt;=0,Y6,"")</f>
         <v/>
       </c>
-      <c r="Z86" s="35">
+      <c r="Z86" s="37">
         <f>IF(Z79&gt;=0,Z6,"")</f>
         <v/>
       </c>
-      <c r="AA86" s="35">
+      <c r="AA86" s="37">
         <f>IF(AA79&gt;=0,AA6,"")</f>
         <v/>
       </c>
-      <c r="AB86" s="35">
+      <c r="AB86" s="37">
         <f>IF(AB79&gt;=0,AB6,"")</f>
         <v/>
       </c>
-      <c r="AC86" s="35">
+      <c r="AC86" s="37">
         <f>IF(AC79&gt;=0,AC6,"")</f>
         <v/>
       </c>
-      <c r="AD86" s="35">
+      <c r="AD86" s="37">
         <f>IF(AD79&gt;=0,AD6,"")</f>
         <v/>
       </c>
-      <c r="AE86" s="35">
+      <c r="AE86" s="37">
         <f>IF(AE79&gt;=0,AE6,"")</f>
         <v/>
       </c>
-      <c r="AF86" s="35">
+      <c r="AF86" s="37">
         <f>IF(AF79&gt;=0,AF6,"")</f>
         <v/>
       </c>
-      <c r="AG86" s="35">
+      <c r="AG86" s="37">
         <f>IF(AG79&gt;=0,AG6,"")</f>
         <v/>
       </c>
-      <c r="AH86" s="35">
+      <c r="AH86" s="37">
         <f>IF(AH79&gt;=0,AH6,"")</f>
         <v/>
       </c>
-      <c r="AI86" s="35">
+      <c r="AI86" s="37">
         <f>IF(AI79&gt;=0,AI6,"")</f>
         <v/>
       </c>
-      <c r="AJ86" s="35">
+      <c r="AJ86" s="37">
         <f>IF(AJ79&gt;=0,AJ6,"")</f>
         <v/>
       </c>
-      <c r="AK86" s="35">
+      <c r="AK86" s="37">
         <f>IF(AK79&gt;=0,AK6,"")</f>
         <v/>
       </c>
-      <c r="AL86" s="35">
+      <c r="AL86" s="37">
         <f>IF(AL79&gt;=0,AL6,"")</f>
         <v/>
       </c>
-      <c r="AM86" s="35">
+      <c r="AM86" s="37">
         <f>IF(AM79&gt;=0,AM6,"")</f>
         <v/>
       </c>
@@ -21303,7 +21504,7 @@
           <t>Select scenario</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
@@ -21320,7 +21521,7 @@
           <t>Scenario index (1=Low, 2=Base, 3=High)</t>
         </is>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="37">
         <f>MATCH(B3,Inputs!$C$83:$E$83,0)</f>
         <v/>
       </c>
@@ -21343,7 +21544,7 @@
           <t>Organic traffic multiplier</t>
         </is>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="41">
         <f>INDEX(Inputs!$C$84:$E$84,$B$4)</f>
         <v/>
       </c>
@@ -21354,7 +21555,7 @@
           <t>Purchase conversion multiplier</t>
         </is>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="41">
         <f>INDEX(Inputs!$C$85:$E$85,$B$4)</f>
         <v/>
       </c>
@@ -21365,7 +21566,7 @@
           <t>Repeat purchase multiplier</t>
         </is>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="41">
         <f>INDEX(Inputs!$C$86:$E$86,$B$4)</f>
         <v/>
       </c>
@@ -21376,7 +21577,7 @@
           <t>Token cost multiplier</t>
         </is>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="41">
         <f>INDEX(Inputs!$C$87:$E$87,$B$4)</f>
         <v/>
       </c>
@@ -21387,7 +21588,7 @@
           <t>Refund / reprint multiplier</t>
         </is>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="41">
         <f>INDEX(Inputs!$C$88:$E$88,$B$4)</f>
         <v/>
       </c>
@@ -21398,7 +21599,7 @@
           <t>Marketing budget multiplier</t>
         </is>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="41">
         <f>INDEX(Inputs!$C$89:$E$89,$B$4)</f>
         <v/>
       </c>
@@ -21409,7 +21610,7 @@
           <t>Print + shipping cost multiplier</t>
         </is>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="41">
         <f>INDEX(Inputs!$C$90:$E$90,$B$4)</f>
         <v/>
       </c>
@@ -21437,7 +21638,7 @@
           <t>Break-even month (sustained: trailing-3M profit stays &gt;= 0)</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="40">
         <f>IF(COUNT(Forecast!$D$85:$AM$85)=0,"Not within 36 mo",MIN(Forecast!$D$85:$AM$85))</f>
         <v/>
       </c>
@@ -21453,7 +21654,7 @@
           <t>First profitable month</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="40">
         <f>IF(COUNT(Forecast!$D$84:$AM$84)=0,"Not within 36 mo",MIN(Forecast!$D$84:$AM$84))</f>
         <v/>
       </c>
@@ -21469,7 +21670,7 @@
           <t>Cash payback month (cumulative net income &gt;= 0)</t>
         </is>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="40">
         <f>IF(COUNT(Forecast!$D$86:$AM$86)=0,"Not within 36 mo",MIN(Forecast!$D$86:$AM$86))</f>
         <v/>
       </c>
@@ -21613,7 +21814,7 @@
           <t>Total orders, 36 months</t>
         </is>
       </c>
-      <c r="B30" s="38">
+      <c r="B30" s="40">
         <f>SUM(Forecast!$D$43:$AM$43)</f>
         <v/>
       </c>
@@ -21661,7 +21862,7 @@
           <t>LTV : blended CAC</t>
         </is>
       </c>
-      <c r="B34" s="41">
+      <c r="B34" s="42">
         <f>IFERROR($B$33/$B$31,0)</f>
         <v/>
       </c>
@@ -21677,7 +21878,7 @@
           <t>LTV : paid CAC</t>
         </is>
       </c>
-      <c r="B35" s="41">
+      <c r="B35" s="42">
         <f>IFERROR($B$33/$B$32,0)</f>
         <v/>
       </c>
@@ -21775,7 +21976,7 @@
           <t>Break-even month (sustained)</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="40">
         <f>Scenarios!$B$16</f>
         <v/>
       </c>
@@ -21786,7 +21987,7 @@
           <t>Cash payback month</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="40">
         <f>Scenarios!$B$18</f>
         <v/>
       </c>
@@ -21885,7 +22086,7 @@
           <t>LTV : blended CAC</t>
         </is>
       </c>
-      <c r="B15" s="41">
+      <c r="B15" s="42">
         <f>Scenarios!$B$34</f>
         <v/>
       </c>
@@ -21896,7 +22097,7 @@
           <t>Orders, 36 months</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="40">
         <f>Scenarios!$B$30</f>
         <v/>
       </c>
@@ -21929,15 +22130,15 @@
           <t>Visits</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="37">
         <f>Forecast!AO30</f>
         <v/>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="37">
         <f>Forecast!AP30</f>
         <v/>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="37">
         <f>Forecast!AQ30</f>
         <v/>
       </c>
@@ -21948,15 +22149,15 @@
           <t>New-customer orders</t>
         </is>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="37">
         <f>Forecast!AO40</f>
         <v/>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="37">
         <f>Forecast!AP40</f>
         <v/>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="37">
         <f>Forecast!AQ40</f>
         <v/>
       </c>
@@ -21967,15 +22168,15 @@
           <t>Total orders</t>
         </is>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="37">
         <f>Forecast!AO43</f>
         <v/>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="37">
         <f>Forecast!AP43</f>
         <v/>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="37">
         <f>Forecast!AQ43</f>
         <v/>
       </c>
